--- a/beer-pour-results.xlsx
+++ b/beer-pour-results.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,20 @@
       <color rgb="00065F46"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009A3412"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +78,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
         <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+        <bgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -101,6 +131,198 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -198,6 +420,1742 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -500,7 +2458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -607,12 +2565,2598 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="66" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="64" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="64" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-42.6</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-54</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>-50.7</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="67" t="inlineStr">
+        <is>
+          <t>DIRTY</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-45.1</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-48.9</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-44.4</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-48.8</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-44.8</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-41.9</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-42.3</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="64" t="inlineStr">
+        <is>
+          <t>SLOW</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-49.4</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-48.5</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-43.6</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-49.7</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-45.2</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-46.7</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-44</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-55.7</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-49.4</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-54.6</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>-54.6</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>-41</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>-51.7</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>-47</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>-47.5</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="64" t="inlineStr">
+        <is>
+          <t>SLOW</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>-53.1</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>-59</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>-58.7</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>-49.2</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>-46.6</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>-47.9</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>-47.7</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>-47.8</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>-46</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="64" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-45.9</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>-45.8</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="64" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>-51.6</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="64" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>-50.5</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="64" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>-52.2</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="64" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>-56.3</v>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="64" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>-56.8</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="64" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>-45.2</v>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="64" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>-42.2</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="64" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>-45</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="64" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>-48.9</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="64" t="inlineStr">
+        <is>
+          <t>SLOW</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="64" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>-46.7</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="64" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>-40.4</v>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="67" t="inlineStr">
+        <is>
+          <t>DIRTY</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="64" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>20260527-170731</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>-46.9</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/beer-pour-results.xlsx
+++ b/beer-pour-results.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +54,14 @@
       <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009A3412"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +104,12 @@
         <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+        <bgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -121,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -154,6 +166,366 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -389,6 +761,3366 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>74</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>79</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>81</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>82</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>84</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>89</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>90</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>91</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>92</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>96</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>105</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId109"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>110</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="110" name="Image 110" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId110"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>111</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="111" name="Image 111" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId111"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="112" name="Image 112" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>113</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId113"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId114"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="115" name="Image 115" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId115"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>116</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="116" name="Image 116" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId116"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>117</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="117" name="Image 117" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId117"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>118</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="118" name="Image 118" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId118"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>119</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="119" name="Image 119" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId119"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>120</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="120" name="Image 120" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId120"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>121</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="121" name="Image 121" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>122</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="122" name="Image 122" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId122"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>123</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="123" name="Image 123" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId123"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>124</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="124" name="Image 124" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId124"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>125</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="125" name="Image 125" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId125"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>126</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="126" name="Image 126" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId126"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -691,7 +4423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -798,7 +4530,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="129" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -843,7 +4575,7 @@
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="129" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -888,7 +4620,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="130" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -929,7 +4661,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="J5" s="129" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -974,7 +4706,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="J6" s="129" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -1005,7 +4737,7 @@
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="114" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1015,6 +4747,4848 @@
           <t>this test was done on purpose</t>
         </is>
       </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>-55.1</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-53.4</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-55.2</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-52.3</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-53.2</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-53</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-48.5</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-52.1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-53.5</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-48.2</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-48.2</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-48.2</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-54.8</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-55.3</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-44.8</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-46.6</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-46.3</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-59</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-61</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-51.9</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-42.7</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-44.9</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>-45.3</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-50.3</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>-50.3</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>-49.6</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>-49.4</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>-52.2</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-52.6</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>-54.6</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>-53.8</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>-53.9</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>-53.4</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="85" t="inlineStr">
+        <is>
+          <t>CROSSREADS</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>-54.9</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>-53</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>-53</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>-54.9</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>-53.4</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>-50.6</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="64" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-54.3</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>-50.5</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="64" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>-53.5</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="64" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>-56.2</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="64" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>-58.9</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="64" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="64" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>-47.3</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="64" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>-54.9</v>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="64" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="64" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>-53.8</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="85" t="inlineStr">
+        <is>
+          <t>CROSSREADS</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60" ht="64" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>-60.8</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="64" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>-52.9</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="64" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="64" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="64" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>-51</v>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>-52.3</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="64" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68" ht="64" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>-53</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="64" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>-52.1</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70" ht="64" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>-43.3</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="64" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>-44.4</v>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72" ht="64" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="64" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>-48.7</v>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr"/>
+      <c r="J73" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74" ht="64" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>-48.2</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="64" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>-53.8</v>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="64" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="6" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78" ht="64" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>-59.7</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="64" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>-51.7</v>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr"/>
+      <c r="J79" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80" ht="64" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>-52.6</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="64" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="85" t="inlineStr">
+        <is>
+          <t>CROSSREADS</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82" ht="64" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="64" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v>-45.1</v>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84" ht="64" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85" ht="64" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>-35.6</v>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>This test run was done deliberately by placing the mugs on the furtherm</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="64" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" ht="64" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>-45.3</v>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88" ht="64" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>-57.4</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="64" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>-57.6</v>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90" ht="64" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>-57.5</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91" ht="64" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>-57.7</v>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr"/>
+      <c r="J91" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92" ht="64" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>-57.7</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93" ht="64" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr"/>
+      <c r="J93" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94" ht="64" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="64" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="6" t="n">
+        <v>-46.8</v>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr"/>
+      <c r="J95" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96" ht="64" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="64" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="6" t="n">
+        <v>-50.4</v>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98" ht="64" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>-55.4</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99" ht="64" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v>-55.7</v>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr"/>
+      <c r="J99" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100" ht="64" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101" ht="64" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v>-60</v>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr"/>
+      <c r="J101" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102" ht="64" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103" ht="64" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="6" t="n">
+        <v>-57.7</v>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr"/>
+      <c r="J103" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104" ht="64" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>-51.8</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105" ht="64" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="6" t="n">
+        <v>-54.6</v>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr"/>
+      <c r="J105" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106" ht="64" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>-53.8</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107" ht="64" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>-51.8</v>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr"/>
+      <c r="J107" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108" ht="64" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>-56.5</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109" ht="64" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="6" t="n">
+        <v>-54.8</v>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr"/>
+      <c r="J109" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110" ht="64" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="114" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111" ht="64" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D111" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="6" t="n">
+        <v>-49.1</v>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr"/>
+      <c r="J111" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112" ht="64" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>-51.9</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113" ht="64" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="6" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr"/>
+      <c r="J113" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114" ht="64" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>-60.4</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115" ht="64" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="6" t="n">
+        <v>-48.9</v>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr"/>
+      <c r="J115" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116" ht="64" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>-55.7</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117" ht="64" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D117" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="6" t="n">
+        <v>-64.7</v>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr"/>
+      <c r="J117" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>SCT S0</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="64" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>-48.5</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119" ht="64" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D119" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="6" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr"/>
+      <c r="J119" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120" ht="64" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>-52.7</v>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121" ht="64" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D121" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="6" t="n">
+        <v>-47.9</v>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122" ht="64" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123" ht="64" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="6" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr"/>
+      <c r="J123" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124" ht="64" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>-46.6</v>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125" ht="64" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="6" t="n">
+        <v>-45.5</v>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr"/>
+      <c r="J125" s="129" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126" ht="64" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>-48.5</v>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="130" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127" ht="64" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>20260528-111856</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>drip_tray_half_full_cup_empty</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="6" t="n">
+        <v>-50.2</v>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr"/>
+      <c r="J127" s="131" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/beer-pour-results.xlsx
+++ b/beer-pour-results.xlsx
@@ -39,6 +39,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="11"/>
     </font>
@@ -46,12 +52,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00065F46"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -82,8 +82,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,14 +94,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -159,373 +159,358 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3981,146 +3966,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>122</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="122" name="Image 122" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId122"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>123</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="123" name="Image 123" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId123"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>124</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="124" name="Image 124" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId124"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>125</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="125" name="Image 125" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId125"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="126" name="Image 126" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId126"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4423,7 +4268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4499,7 +4344,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20260528-105206</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -4508,43 +4353,33 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant1</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>-52</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6F76</t>
-        </is>
-      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J2" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>SCT S1</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>20260528-105206</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4553,43 +4388,29 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>6E6FD6 -&gt; ant0</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
-        <v>-57.4</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6</t>
-        </is>
-      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>SCT S0</t>
-        </is>
-      </c>
+      <c r="J3" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="64" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20260528-105206</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4598,31 +4419,31 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-54.6</v>
+        <v>-53.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J4" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -4630,7 +4451,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>20260528-105206</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4639,43 +4460,39 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>66</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-47.8</v>
+        <v>-49.7</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="129" t="inlineStr">
+      <c r="J5" s="115" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>this test was done on pourpose to test the verdict system</t>
-        </is>
-      </c>
+      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="64" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>20260528-105206</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -4684,31 +4501,21 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6E0AE6 -&gt; ant1, 6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1, 6E74E6 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>-62.1</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E74E6, E2801191A5040076596E6FD6, E2801191A5040076596E0AE6</t>
-        </is>
-      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J6" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -4716,7 +4523,7 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>20260528-105206</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4725,33 +4532,39 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
+        <v>-53.8</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>this test was done on purpose</t>
-        </is>
-      </c>
+      <c r="J7" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4765,26 +4578,16 @@
       <c r="D8" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>-55.1</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
-        </is>
-      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J8" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -4792,7 +4595,7 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -4806,26 +4609,16 @@
       <c r="D9" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
-        </is>
-      </c>
+      <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>-53.4</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
-        </is>
-      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J9" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr"/>
@@ -4833,7 +4626,7 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4847,26 +4640,16 @@
       <c r="D10" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
-        </is>
-      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>-55.2</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
-        </is>
-      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J10" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -4874,7 +4657,7 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -4888,26 +4671,16 @@
       <c r="D11" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
-        </is>
-      </c>
+      <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <v>-52.3</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
-        </is>
-      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J11" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr"/>
@@ -4915,7 +4688,7 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4924,31 +4697,31 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-53.2</v>
+        <v>-49.1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J12" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -4956,7 +4729,7 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -4965,21 +4738,31 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
+      <c r="G13" s="6" t="n">
+        <v>-49.4</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J13" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr"/>
@@ -4987,7 +4770,7 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4996,31 +4779,31 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-53</v>
+        <v>-46.4</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J14" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
@@ -5028,7 +4811,7 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -5037,31 +4820,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>66</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-48.5</v>
+        <v>-46.2</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J15" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr"/>
@@ -5069,7 +4852,7 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -5078,31 +4861,31 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-52.1</v>
+        <v>-44.6</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J16" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -5110,7 +4893,7 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -5119,29 +4902,29 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-53.5</v>
+        <v>-49.4</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="130" t="inlineStr">
+      <c r="J17" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5151,7 +4934,7 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -5167,36 +4950,32 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-48.2</v>
+        <v>-51.9</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="130" t="inlineStr">
+      <c r="J18" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="64" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -5208,7 +4987,7 @@
         <v>175</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -5219,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-48.2</v>
+        <v>-53.4</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -5227,17 +5006,21 @@
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="130" t="inlineStr">
+      <c r="J19" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="64" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -5253,14 +5036,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-48.2</v>
+        <v>-50.7</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -5268,17 +5051,21 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>CROSSREADS</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -5290,36 +5077,40 @@
         <v>175</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-54.8</v>
+        <v>-49.1</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr"/>
+      <c r="J21" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>SCT s0</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="64" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -5328,29 +5119,29 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-55.3</v>
+        <v>-46.2</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="130" t="inlineStr">
+      <c r="J22" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5360,7 +5151,7 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -5369,29 +5160,29 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>66</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-44.8</v>
+        <v>-57.4</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="130" t="inlineStr">
+      <c r="J23" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5401,7 +5192,7 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -5410,10 +5201,10 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -5424,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-46.6</v>
+        <v>-47.1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -5432,7 +5223,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="130" t="inlineStr">
+      <c r="J24" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5442,7 +5233,7 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -5451,29 +5242,29 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>66</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-46.3</v>
+        <v>-57.6</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="130" t="inlineStr">
+      <c r="J25" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5483,7 +5274,7 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5492,7 +5283,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>66</v>
@@ -5506,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-59</v>
+        <v>-41.7</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -5514,7 +5305,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="130" t="inlineStr">
+      <c r="J26" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5524,7 +5315,7 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -5533,31 +5324,31 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>66</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-61</v>
+        <v>-48.4</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J27" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr"/>
@@ -5565,7 +5356,7 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -5577,7 +5368,7 @@
         <v>316</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -5588,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-51.9</v>
+        <v>-51.7</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -5596,7 +5387,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="130" t="inlineStr">
+      <c r="J28" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5606,7 +5397,7 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -5618,28 +5409,28 @@
         <v>316</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-42.7</v>
+        <v>-54.8</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J29" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr"/>
@@ -5647,7 +5438,7 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -5659,7 +5450,7 @@
         <v>316</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -5670,7 +5461,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-44.6</v>
+        <v>-52.9</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -5678,7 +5469,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="130" t="inlineStr">
+      <c r="J30" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5688,7 +5479,7 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -5700,26 +5491,26 @@
         <v>316</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-44.9</v>
+        <v>-54.3</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="130" t="inlineStr">
+      <c r="J31" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5729,7 +5520,7 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -5738,29 +5529,29 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>-45.3</v>
+        <v>-54.8</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="130" t="inlineStr">
+      <c r="J32" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5770,7 +5561,7 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -5779,29 +5570,29 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>62</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-50.3</v>
+        <v>-57.7</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="130" t="inlineStr">
+      <c r="J33" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5811,7 +5602,7 @@
     <row r="34" ht="64" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -5820,29 +5611,29 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>-50.3</v>
+        <v>-54.9</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="130" t="inlineStr">
+      <c r="J34" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5852,7 +5643,7 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -5861,29 +5652,29 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-49.6</v>
+        <v>-56.4</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="130" t="inlineStr">
+      <c r="J35" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5893,7 +5684,7 @@
     <row r="36" ht="64" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -5902,29 +5693,29 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-49.4</v>
+        <v>-61.6</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="130" t="inlineStr">
+      <c r="J36" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5934,7 +5725,7 @@
     <row r="37" ht="64" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -5943,31 +5734,31 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>66</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-52.2</v>
+        <v>-57</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J37" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr"/>
@@ -5975,7 +5766,7 @@
     <row r="38" ht="64" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5987,7 +5778,7 @@
         <v>30</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -5998,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>-52.6</v>
+        <v>-57.2</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -6006,7 +5797,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="130" t="inlineStr">
+      <c r="J38" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6016,7 +5807,7 @@
     <row r="39" ht="64" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -6028,28 +5819,28 @@
         <v>30</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-54.6</v>
+        <v>-60.6</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J39" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr"/>
@@ -6057,7 +5848,7 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -6069,18 +5860,18 @@
         <v>30</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-53.8</v>
+        <v>-56.7</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -6088,9 +5879,9 @@
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J40" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
@@ -6098,7 +5889,7 @@
     <row r="41" ht="64" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -6110,18 +5901,18 @@
         <v>30</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-53.9</v>
+        <v>-53.6</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
@@ -6129,9 +5920,9 @@
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J41" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr"/>
@@ -6139,7 +5930,7 @@
     <row r="42" ht="64" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -6148,21 +5939,21 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>-53.4</v>
+        <v>-55.3</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -6170,17 +5961,21 @@
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="85" t="inlineStr">
-        <is>
-          <t>CROSSREADS</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="J42" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="64" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -6189,39 +5984,43 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-54.9</v>
+        <v>-55.5</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr"/>
+      <c r="J43" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="64" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -6230,29 +6029,29 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>-53</v>
+        <v>-54.2</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="130" t="inlineStr">
+      <c r="J44" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6262,7 +6061,7 @@
     <row r="45" ht="64" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -6271,21 +6070,21 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>64</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-53</v>
+        <v>-59.3</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
@@ -6293,9 +6092,9 @@
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J45" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr"/>
@@ -6303,7 +6102,7 @@
     <row r="46" ht="64" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6312,21 +6111,21 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-54.9</v>
+        <v>-59</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -6334,9 +6133,9 @@
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J46" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -6344,7 +6143,7 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -6353,7 +6152,7 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>66</v>
@@ -6367,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-53.4</v>
+        <v>-59.1</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
@@ -6375,7 +6174,7 @@
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="130" t="inlineStr">
+      <c r="J47" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6385,7 +6184,7 @@
     <row r="48" ht="64" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6397,30 +6196,36 @@
         <v>175</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="G48" s="3" t="n">
+        <v>-58.6</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="J48" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="64" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -6432,26 +6237,26 @@
         <v>175</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-50.6</v>
+        <v>-58.1</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="130" t="inlineStr">
+      <c r="J49" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6461,7 +6266,7 @@
     <row r="50" ht="64" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -6473,26 +6278,26 @@
         <v>175</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-54.3</v>
+        <v>-56.5</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="129" t="inlineStr">
+      <c r="J50" s="115" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -6502,7 +6307,7 @@
     <row r="51" ht="64" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -6514,28 +6319,28 @@
         <v>175</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-50.5</v>
+        <v>-56</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J51" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr"/>
@@ -6543,7 +6348,7 @@
     <row r="52" ht="64" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -6552,31 +6357,31 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-53.5</v>
+        <v>-49.1</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J52" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
@@ -6584,7 +6389,7 @@
     <row r="53" ht="64" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -6593,10 +6398,10 @@
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
@@ -6607,15 +6412,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-56.2</v>
+        <v>-54.3</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="130" t="inlineStr">
+      <c r="J53" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6625,7 +6430,7 @@
     <row r="54" ht="64" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6634,43 +6439,39 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>64</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>-58.9</v>
+        <v>-55.2</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="J54" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55" ht="64" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -6679,21 +6480,31 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="E55" s="5" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
+      <c r="G55" s="6" t="n">
+        <v>-51.7</v>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J55" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr"/>
@@ -6701,7 +6512,7 @@
     <row r="56" ht="64" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6710,31 +6521,31 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-47.3</v>
+        <v>-51.2</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J56" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
@@ -6742,7 +6553,7 @@
     <row r="57" ht="64" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -6751,21 +6562,21 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>62</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-54.9</v>
+        <v>-51.6</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
@@ -6773,7 +6584,7 @@
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="130" t="inlineStr">
+      <c r="J57" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6783,7 +6594,7 @@
     <row r="58" ht="64" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6795,18 +6606,28 @@
         <v>316</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="G58" s="3" t="n">
+        <v>-54.2</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J58" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
@@ -6814,7 +6635,7 @@
     <row r="59" ht="64" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -6826,28 +6647,28 @@
         <v>316</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-53.8</v>
+        <v>-58</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="85" t="inlineStr">
-        <is>
-          <t>CROSSREADS</t>
+      <c r="J59" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr"/>
@@ -6855,7 +6676,7 @@
     <row r="60" ht="64" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6871,24 +6692,24 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>-60.8</v>
+        <v>-51.4</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J60" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
@@ -6896,7 +6717,7 @@
     <row r="61" ht="64" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -6908,18 +6729,28 @@
         <v>316</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="E61" s="5" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F61" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="6" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr"/>
+      <c r="G61" s="6" t="n">
+        <v>-54.1</v>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J61" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr"/>
@@ -6927,40 +6758,30 @@
     <row r="62" ht="64" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant0</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="n">
-        <v>-52.9</v>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J62" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
@@ -6968,16 +6789,16 @@
     <row r="63" ht="64" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D63" s="6" t="n">
         <v>66</v>
@@ -6989,33 +6810,29 @@
       <c r="G63" s="6" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="114" t="inlineStr">
+      <c r="J63" s="101" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K63" s="5" t="inlineStr"/>
     </row>
     <row r="64" ht="64" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="3" t="n">
@@ -7024,7 +6841,7 @@
       <c r="G64" s="3" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="114" t="inlineStr">
+      <c r="J64" s="101" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7034,40 +6851,30 @@
     <row r="65" ht="64" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D65" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant1</t>
-        </is>
-      </c>
+      <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="6" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J65" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr"/>
@@ -7075,40 +6882,30 @@
     <row r="66" ht="64" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="3" t="n">
-        <v>-52.3</v>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J66" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
@@ -7116,40 +6913,30 @@
     <row r="67" ht="64" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr"/>
       <c r="F67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="6" t="n">
-        <v>-51.1</v>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
+      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J67" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr"/>
@@ -7157,7 +6944,7 @@
     <row r="68" ht="64" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -7171,26 +6958,16 @@
       <c r="D68" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>6E6FD6 -&gt; ant1</t>
-        </is>
-      </c>
+      <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G68" s="3" t="n">
-        <v>-53</v>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6</t>
-        </is>
-      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J68" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
@@ -7198,7 +6975,7 @@
     <row r="69" ht="64" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -7212,26 +6989,16 @@
       <c r="D69" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>6E6FD6 -&gt; ant1</t>
-        </is>
-      </c>
+      <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G69" s="6" t="n">
-        <v>-52.1</v>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6</t>
-        </is>
-      </c>
+      <c r="G69" s="6" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J69" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr"/>
@@ -7239,7 +7006,7 @@
     <row r="70" ht="64" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -7253,26 +7020,16 @@
       <c r="D70" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>6E6FD6 -&gt; ant1</t>
-        </is>
-      </c>
+      <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G70" s="3" t="n">
-        <v>-43.3</v>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6</t>
-        </is>
-      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J70" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
@@ -7280,7 +7037,7 @@
     <row r="71" ht="64" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -7294,26 +7051,16 @@
       <c r="D71" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>6E6FD6 -&gt; ant1</t>
-        </is>
-      </c>
+      <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G71" s="6" t="n">
-        <v>-44.4</v>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6</t>
-        </is>
-      </c>
+      <c r="G71" s="6" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J71" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr"/>
@@ -7321,7 +7068,7 @@
     <row r="72" ht="64" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -7330,29 +7077,43 @@
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D72" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="G72" s="3" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
+      <c r="J72" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="64" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -7361,29 +7122,29 @@
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D73" s="6" t="n">
         <v>66</v>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1</t>
         </is>
       </c>
       <c r="F73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>-48.7</v>
+        <v>-60</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="129" t="inlineStr">
+      <c r="J73" s="115" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -7393,7 +7154,7 @@
     <row r="74" ht="64" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -7402,43 +7163,39 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>-48.2</v>
+        <v>-53.6</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="129" t="inlineStr">
+      <c r="J74" s="115" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K74" s="2" t="inlineStr"/>
     </row>
     <row r="75" ht="64" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -7447,29 +7204,29 @@
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0</t>
         </is>
       </c>
       <c r="F75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>-53.8</v>
+        <v>-55.4</v>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="129" t="inlineStr">
+      <c r="J75" s="115" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -7479,7 +7236,7 @@
     <row r="76" ht="64" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -7488,21 +7245,31 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F76" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="G76" s="3" t="n">
+        <v>-38.3</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J76" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
@@ -7510,7 +7277,7 @@
     <row r="77" ht="64" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -7519,21 +7286,31 @@
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D77" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F77" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="6" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr"/>
+      <c r="G77" s="6" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
       <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J77" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr"/>
@@ -7541,7 +7318,7 @@
     <row r="78" ht="64" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -7553,7 +7330,7 @@
         <v>175</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -7564,7 +7341,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>-59.7</v>
+        <v>-47.6</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -7572,7 +7349,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="130" t="inlineStr">
+      <c r="J78" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7582,7 +7359,7 @@
     <row r="79" ht="64" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -7605,15 +7382,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>-51.7</v>
+        <v>-57.3</v>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="130" t="inlineStr">
+      <c r="J79" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7623,7 +7400,7 @@
     <row r="80" ht="64" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -7635,28 +7412,28 @@
         <v>175</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>-52.6</v>
+        <v>-49.8</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J80" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
@@ -7664,7 +7441,7 @@
     <row r="81" ht="64" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -7676,28 +7453,28 @@
         <v>175</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>-61.8</v>
+        <v>-41.7</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="85" t="inlineStr">
-        <is>
-          <t>CROSSREADS</t>
+      <c r="J81" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr"/>
@@ -7705,7 +7482,7 @@
     <row r="82" ht="64" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -7714,39 +7491,43 @@
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-43</v>
+        <v>-59</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="130" t="inlineStr">
+      <c r="J82" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="64" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -7755,7 +7536,7 @@
         </is>
       </c>
       <c r="C83" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D83" s="6" t="n">
         <v>66</v>
@@ -7769,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>-45.1</v>
+        <v>-58.8</v>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
@@ -7777,7 +7558,7 @@
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="130" t="inlineStr">
+      <c r="J83" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7787,7 +7568,7 @@
     <row r="84" ht="64" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -7796,7 +7577,7 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D84" s="3" t="n">
         <v>66</v>
@@ -7810,25 +7591,29 @@
         <v>0</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>-48.3</v>
+        <v>-42.2</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="130" t="inlineStr">
+      <c r="J84" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="64" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -7837,21 +7622,21 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F85" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>-35.6</v>
+        <v>-42.5</v>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
@@ -7859,21 +7644,17 @@
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="130" t="inlineStr">
+      <c r="J85" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>This test run was done deliberately by placing the mugs on the furtherm</t>
-        </is>
-      </c>
+      <c r="K85" s="5" t="inlineStr"/>
     </row>
     <row r="86" ht="64" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -7882,31 +7663,31 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>-40.8</v>
+        <v>-53</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J86" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
@@ -7914,7 +7695,7 @@
     <row r="87" ht="64" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -7923,10 +7704,10 @@
         </is>
       </c>
       <c r="C87" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
@@ -7937,15 +7718,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>-45.3</v>
+        <v>-47.1</v>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="130" t="inlineStr">
+      <c r="J87" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7955,7 +7736,7 @@
     <row r="88" ht="64" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -7978,15 +7759,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>-57.4</v>
+        <v>-37</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="130" t="inlineStr">
+      <c r="J88" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7996,7 +7777,7 @@
     <row r="89" ht="64" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -8008,26 +7789,26 @@
         <v>316</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F89" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>-57.6</v>
+        <v>-47.3</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="130" t="inlineStr">
+      <c r="J89" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8037,7 +7818,7 @@
     <row r="90" ht="64" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -8053,22 +7834,22 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>-57.5</v>
+        <v>-46.7</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="130" t="inlineStr">
+      <c r="J90" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8078,7 +7859,7 @@
     <row r="91" ht="64" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -8101,7 +7882,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>-57.7</v>
+        <v>-41.5</v>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
@@ -8109,7 +7890,7 @@
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="130" t="inlineStr">
+      <c r="J91" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8119,7 +7900,7 @@
     <row r="92" ht="64" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -8128,29 +7909,29 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-57.7</v>
+        <v>-62.3</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="130" t="inlineStr">
+      <c r="J92" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8160,7 +7941,7 @@
     <row r="93" ht="64" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -8169,29 +7950,29 @@
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>-32.9</v>
+        <v>-61.5</v>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="130" t="inlineStr">
+      <c r="J93" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8201,7 +7982,7 @@
     <row r="94" ht="64" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -8210,29 +7991,29 @@
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>-43.1</v>
+        <v>-58.6</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="130" t="inlineStr">
+      <c r="J94" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8242,7 +8023,7 @@
     <row r="95" ht="64" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -8251,29 +8032,29 @@
         </is>
       </c>
       <c r="C95" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F95" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>-46.8</v>
+        <v>-57.2</v>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="130" t="inlineStr">
+      <c r="J95" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8283,7 +8064,7 @@
     <row r="96" ht="64" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -8292,43 +8073,29 @@
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>6E6FD6 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="3" t="n">
-        <v>-35</v>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6</t>
-        </is>
-      </c>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
+      <c r="J96" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="64" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -8337,31 +8104,21 @@
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="D97" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant0</t>
-        </is>
-      </c>
+      <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G97" s="6" t="n">
-        <v>-50.4</v>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6F76</t>
-        </is>
-      </c>
+      <c r="G97" s="6" t="inlineStr"/>
+      <c r="H97" s="5" t="inlineStr"/>
       <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J97" s="101" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr"/>
@@ -8369,7 +8126,7 @@
     <row r="98" ht="64" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -8381,28 +8138,28 @@
         <v>30</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-55.4</v>
+        <v>-59.1</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J98" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
@@ -8410,7 +8167,7 @@
     <row r="99" ht="64" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -8422,26 +8179,26 @@
         <v>30</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F99" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>-55.7</v>
+        <v>-59.6</v>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="130" t="inlineStr">
+      <c r="J99" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8451,7 +8208,7 @@
     <row r="100" ht="64" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -8463,28 +8220,28 @@
         <v>30</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-56.6</v>
+        <v>-61.2</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J100" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
@@ -8492,7 +8249,7 @@
     <row r="101" ht="64" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -8504,26 +8261,26 @@
         <v>30</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F101" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>-60</v>
+        <v>-60.7</v>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="130" t="inlineStr">
+      <c r="J101" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8533,7 +8290,7 @@
     <row r="102" ht="64" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -8542,31 +8299,31 @@
         </is>
       </c>
       <c r="C102" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>-61.8</v>
+        <v>-56.6</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J102" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
@@ -8574,7 +8331,7 @@
     <row r="103" ht="64" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -8583,29 +8340,29 @@
         </is>
       </c>
       <c r="C103" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F103" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>-57.7</v>
+        <v>-56.5</v>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr"/>
-      <c r="J103" s="130" t="inlineStr">
+      <c r="J103" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8615,7 +8372,7 @@
     <row r="104" ht="64" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -8624,10 +8381,10 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -8638,7 +8395,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>-51.8</v>
+        <v>-57.7</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -8646,7 +8403,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="130" t="inlineStr">
+      <c r="J104" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8656,7 +8413,7 @@
     <row r="105" ht="64" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -8665,29 +8422,29 @@
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F105" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>-54.6</v>
+        <v>-58.1</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr"/>
-      <c r="J105" s="130" t="inlineStr">
+      <c r="J105" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8697,7 +8454,7 @@
     <row r="106" ht="64" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -8706,7 +8463,7 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>66</v>
@@ -8720,7 +8477,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-53.8</v>
+        <v>-60.4</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -8728,7 +8485,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="130" t="inlineStr">
+      <c r="J106" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8738,7 +8495,7 @@
     <row r="107" ht="64" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -8747,10 +8504,10 @@
         </is>
       </c>
       <c r="C107" s="6" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
@@ -8761,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>-51.8</v>
+        <v>-55.2</v>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
@@ -8769,7 +8526,7 @@
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr"/>
-      <c r="J107" s="130" t="inlineStr">
+      <c r="J107" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8779,7 +8536,7 @@
     <row r="108" ht="64" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -8795,7 +8552,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -8806,11 +8563,11 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="130" t="inlineStr">
+      <c r="J108" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8820,7 +8577,7 @@
     <row r="109" ht="64" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -8832,26 +8589,26 @@
         <v>175</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F109" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>-54.8</v>
+        <v>-53.8</v>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr"/>
-      <c r="J109" s="130" t="inlineStr">
+      <c r="J109" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8861,7 +8618,7 @@
     <row r="110" ht="64" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -8875,16 +8632,26 @@
       <c r="D110" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="3" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
+      <c r="G110" s="3" t="n">
+        <v>-56.9</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="114" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J110" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
@@ -8892,7 +8659,7 @@
     <row r="111" ht="64" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -8904,28 +8671,28 @@
         <v>175</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F111" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>-49.1</v>
+        <v>-56</v>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr"/>
-      <c r="J111" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J111" s="115" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr"/>
@@ -8933,7 +8700,7 @@
     <row r="112" ht="64" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -8942,10 +8709,10 @@
         </is>
       </c>
       <c r="C112" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -8956,7 +8723,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-51.9</v>
+        <v>-54.8</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -8964,7 +8731,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="130" t="inlineStr">
+      <c r="J112" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8974,7 +8741,7 @@
     <row r="113" ht="64" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -8983,10 +8750,10 @@
         </is>
       </c>
       <c r="C113" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
@@ -8997,7 +8764,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>-58.4</v>
+        <v>-67.2</v>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
@@ -9005,7 +8772,7 @@
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="130" t="inlineStr">
+      <c r="J113" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9015,7 +8782,7 @@
     <row r="114" ht="64" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -9024,10 +8791,10 @@
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -9038,7 +8805,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>-60.4</v>
+        <v>-66.2</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -9046,7 +8813,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="130" t="inlineStr">
+      <c r="J114" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9056,7 +8823,7 @@
     <row r="115" ht="64" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -9065,10 +8832,10 @@
         </is>
       </c>
       <c r="C115" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
@@ -9079,15 +8846,15 @@
         <v>0</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>-48.9</v>
+        <v>-53.9</v>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr"/>
-      <c r="J115" s="130" t="inlineStr">
+      <c r="J115" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9097,7 +8864,7 @@
     <row r="116" ht="64" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -9106,29 +8873,29 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>-55.7</v>
+        <v>-54.2</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="130" t="inlineStr">
+      <c r="J116" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9138,7 +8905,7 @@
     <row r="117" ht="64" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -9147,43 +8914,39 @@
         </is>
       </c>
       <c r="C117" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D117" s="6" t="n">
         <v>66</v>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F117" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>-64.7</v>
+        <v>-53.8</v>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr"/>
-      <c r="J117" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr">
-        <is>
-          <t>SCT S0</t>
-        </is>
-      </c>
+      <c r="J117" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr"/>
     </row>
     <row r="118" ht="64" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -9195,26 +8958,26 @@
         <v>316</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>-48.5</v>
+        <v>-53.9</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="130" t="inlineStr">
+      <c r="J118" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9224,7 +8987,7 @@
     <row r="119" ht="64" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -9247,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>-58.4</v>
+        <v>-54.2</v>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
@@ -9255,7 +9018,7 @@
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr"/>
-      <c r="J119" s="130" t="inlineStr">
+      <c r="J119" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9265,7 +9028,7 @@
     <row r="120" ht="64" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -9277,26 +9040,26 @@
         <v>316</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>-52.7</v>
+        <v>-54.1</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="130" t="inlineStr">
+      <c r="J120" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9306,7 +9069,7 @@
     <row r="121" ht="64" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -9318,28 +9081,28 @@
         <v>316</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F121" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>-47.9</v>
+        <v>-54.1</v>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr"/>
-      <c r="J121" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J121" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr"/>
@@ -9347,7 +9110,7 @@
     <row r="122" ht="64" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>20260528-111856</t>
+          <t>20260528-124145</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -9359,236 +9122,35 @@
         <v>316</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>-48</v>
+        <v>-54.8</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123" ht="64" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>20260528-111856</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_half_full_cup_empty</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D123" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F123" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="6" t="n">
-        <v>-51.1</v>
-      </c>
-      <c r="H123" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I123" s="5" t="inlineStr"/>
-      <c r="J123" s="130" t="inlineStr">
+      <c r="J122" s="126" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K123" s="5" t="inlineStr"/>
-    </row>
-    <row r="124" ht="64" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>20260528-111856</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_half_full_cup_empty</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>-46.6</v>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125" ht="64" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>20260528-111856</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_half_full_cup_empty</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D125" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F125" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="6" t="n">
-        <v>-45.5</v>
-      </c>
-      <c r="H125" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I125" s="5" t="inlineStr"/>
-      <c r="J125" s="129" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr"/>
-    </row>
-    <row r="126" ht="64" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>20260528-111856</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_half_full_cup_empty</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="130" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127" ht="64" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>20260528-111856</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_half_full_cup_empty</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D127" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F127" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" s="6" t="n">
-        <v>-50.2</v>
-      </c>
-      <c r="H127" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I127" s="5" t="inlineStr"/>
-      <c r="J127" s="131" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>these test runs were done with an metal fin in the middle</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/beer-pour-results.xlsx
+++ b/beer-pour-results.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,14 +54,8 @@
       <color rgb="00065F46"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="009A3412"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -104,12 +98,6 @@
         <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEDD5"/>
-        <bgColor rgb="00FFEDD5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -133,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -159,27 +147,207 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -204,7 +372,40 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -216,24 +417,33 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -253,231 +463,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3938,34 +3923,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId120"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>121</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="121" name="Image 121" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4268,7 +4225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4344,7 +4301,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -4365,21 +4322,17 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="101" t="inlineStr">
+      <c r="J2" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="64" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4400,7 +4353,7 @@
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="101" t="inlineStr">
+      <c r="J3" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4410,7 +4363,7 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4426,22 +4379,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0</t>
+          <t>6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-53.1</v>
+        <v>-55.6</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="115" t="inlineStr">
+      <c r="J4" s="105" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -4451,7 +4404,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4465,26 +4418,16 @@
       <c r="D5" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant1</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>-49.7</v>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6F76</t>
-        </is>
-      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J5" s="74" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr"/>
@@ -4492,7 +4435,7 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -4513,17 +4456,21 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="101" t="inlineStr">
+      <c r="J6" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4537,34 +4484,28 @@
       <c r="D7" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant1</t>
-        </is>
-      </c>
+      <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>-53.8</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6F76</t>
-        </is>
-      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr"/>
+      <c r="J7" s="74" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4585,7 +4526,7 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="101" t="inlineStr">
+      <c r="J8" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4595,7 +4536,7 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -4616,7 +4557,7 @@
       <c r="G9" s="6" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="101" t="inlineStr">
+      <c r="J9" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4626,7 +4567,7 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4647,7 +4588,7 @@
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="101" t="inlineStr">
+      <c r="J10" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4657,7 +4598,7 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -4678,7 +4619,7 @@
       <c r="G11" s="6" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="101" t="inlineStr">
+      <c r="J11" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4688,7 +4629,7 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4704,32 +4645,36 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-49.1</v>
+        <v>-49.6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="125" t="inlineStr">
+      <c r="J12" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -4741,7 +4686,7 @@
         <v>175</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -4752,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-49.4</v>
+        <v>-53.7</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -4760,17 +4705,21 @@
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="125" t="inlineStr">
+      <c r="J13" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="64" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4782,7 +4731,7 @@
         <v>175</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -4793,25 +4742,29 @@
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-46.4</v>
+        <v>-51.5</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="125" t="inlineStr">
+      <c r="J14" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -4827,14 +4780,14 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-46.2</v>
+        <v>-52.2</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -4842,7 +4795,7 @@
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="125" t="inlineStr">
+      <c r="J15" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4852,7 +4805,7 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -4864,7 +4817,7 @@
         <v>175</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -4875,15 +4828,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-44.6</v>
+        <v>-51.9</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="125" t="inlineStr">
+      <c r="J16" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4893,7 +4846,7 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -4916,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-49.4</v>
+        <v>-48.7</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -4924,7 +4877,7 @@
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="125" t="inlineStr">
+      <c r="J17" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4934,7 +4887,7 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -4946,28 +4899,28 @@
         <v>175</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-51.9</v>
+        <v>-48.2</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J18" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -4975,7 +4928,7 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -4987,40 +4940,36 @@
         <v>175</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-53.4</v>
+        <v>-50.3</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="125" t="inlineStr">
+      <c r="J19" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K19" s="5" t="inlineStr"/>
     </row>
     <row r="20" ht="64" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -5036,14 +4985,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-50.7</v>
+        <v>-47</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -5051,21 +5000,17 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="24" t="inlineStr">
-        <is>
-          <t>CROSSREADS</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
+      <c r="J20" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -5077,40 +5022,36 @@
         <v>175</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-49.1</v>
+        <v>-51.4</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>SCT s0</t>
-        </is>
-      </c>
+      <c r="J21" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="64" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -5126,22 +5067,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-46.2</v>
+        <v>-57.5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="125" t="inlineStr">
+      <c r="J22" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5151,7 +5092,7 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -5174,7 +5115,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-57.4</v>
+        <v>-46.4</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -5182,7 +5123,7 @@
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="125" t="inlineStr">
+      <c r="J23" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5192,7 +5133,7 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -5204,7 +5145,7 @@
         <v>316</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-47.1</v>
+        <v>-47.8</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -5223,7 +5164,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="125" t="inlineStr">
+      <c r="J24" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5233,7 +5174,7 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -5256,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-57.6</v>
+        <v>-45.2</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -5264,7 +5205,7 @@
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="125" t="inlineStr">
+      <c r="J25" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5274,7 +5215,7 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5286,26 +5227,26 @@
         <v>316</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-41.7</v>
+        <v>-53.6</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="125" t="inlineStr">
+      <c r="J26" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5315,7 +5256,7 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -5331,22 +5272,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-48.4</v>
+        <v>-48.5</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="125" t="inlineStr">
+      <c r="J27" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5356,7 +5297,7 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -5368,7 +5309,7 @@
         <v>316</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-51.7</v>
+        <v>-53.2</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -5387,7 +5328,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="125" t="inlineStr">
+      <c r="J28" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5397,7 +5338,7 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -5409,28 +5350,28 @@
         <v>316</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-54.8</v>
+        <v>-53.7</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J29" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr"/>
@@ -5438,7 +5379,7 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -5450,26 +5391,26 @@
         <v>316</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-52.9</v>
+        <v>-46.1</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="125" t="inlineStr">
+      <c r="J30" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5479,7 +5420,7 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -5491,7 +5432,7 @@
         <v>316</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -5502,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-54.3</v>
+        <v>-50</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -5510,7 +5451,7 @@
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="125" t="inlineStr">
+      <c r="J31" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5520,7 +5461,7 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -5536,14 +5477,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>-54.8</v>
+        <v>-60.7</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -5551,7 +5492,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="125" t="inlineStr">
+      <c r="J32" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5561,7 +5502,7 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -5573,26 +5514,26 @@
         <v>30</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-57.7</v>
+        <v>-60.6</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="125" t="inlineStr">
+      <c r="J33" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5602,7 +5543,7 @@
     <row r="34" ht="64" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -5614,26 +5555,26 @@
         <v>30</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>-54.9</v>
+        <v>-54.1</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="125" t="inlineStr">
+      <c r="J34" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5643,7 +5584,7 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -5655,18 +5596,18 @@
         <v>30</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-56.4</v>
+        <v>-54.9</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -5674,7 +5615,7 @@
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="125" t="inlineStr">
+      <c r="J35" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5684,7 +5625,7 @@
     <row r="36" ht="64" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -5696,26 +5637,26 @@
         <v>30</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-61.6</v>
+        <v>-56.2</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="125" t="inlineStr">
+      <c r="J36" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5725,7 +5666,7 @@
     <row r="37" ht="64" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -5741,24 +5682,24 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-57</v>
+        <v>-58.9</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J37" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr"/>
@@ -5766,7 +5707,7 @@
     <row r="38" ht="64" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5789,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>-57.2</v>
+        <v>-57.8</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -5797,7 +5738,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="125" t="inlineStr">
+      <c r="J38" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5807,7 +5748,7 @@
     <row r="39" ht="64" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -5819,28 +5760,28 @@
         <v>30</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-60.6</v>
+        <v>-58.3</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J39" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr"/>
@@ -5848,7 +5789,7 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -5860,28 +5801,28 @@
         <v>30</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-56.7</v>
+        <v>-58</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J40" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
@@ -5889,7 +5830,7 @@
     <row r="41" ht="64" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -5901,7 +5842,7 @@
         <v>30</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -5912,15 +5853,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-53.6</v>
+        <v>-59.1</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="125" t="inlineStr">
+      <c r="J41" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5930,7 +5871,7 @@
     <row r="42" ht="64" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -5946,24 +5887,24 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>-55.3</v>
+        <v>-54.4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J42" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -5975,7 +5916,7 @@
     <row r="43" ht="64" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -5991,24 +5932,24 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-55.5</v>
+        <v>-54.2</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J43" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -6020,7 +5961,7 @@
     <row r="44" ht="64" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -6032,7 +5973,7 @@
         <v>175</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -6043,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>-54.2</v>
+        <v>-53.3</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -6051,17 +5992,21 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="125" t="inlineStr">
+      <c r="J44" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="64" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -6073,7 +6018,7 @@
         <v>175</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -6084,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-59.3</v>
+        <v>-51</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
@@ -6092,7 +6037,7 @@
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="125" t="inlineStr">
+      <c r="J45" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6102,7 +6047,7 @@
     <row r="46" ht="64" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6114,28 +6059,28 @@
         <v>175</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-59</v>
+        <v>-53.5</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J46" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -6143,7 +6088,7 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -6155,7 +6100,7 @@
         <v>175</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
@@ -6166,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-59.1</v>
+        <v>-56.8</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
@@ -6174,7 +6119,7 @@
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="125" t="inlineStr">
+      <c r="J47" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6184,7 +6129,7 @@
     <row r="48" ht="64" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6196,28 +6141,28 @@
         <v>175</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>-58.6</v>
+        <v>-57.2</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J48" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
@@ -6225,7 +6170,7 @@
     <row r="49" ht="64" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -6237,28 +6182,28 @@
         <v>175</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-58.1</v>
+        <v>-57.5</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J49" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr"/>
@@ -6266,7 +6211,7 @@
     <row r="50" ht="64" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -6278,28 +6223,28 @@
         <v>175</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-56.5</v>
+        <v>-59.3</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J50" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
@@ -6307,7 +6252,7 @@
     <row r="51" ht="64" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -6323,22 +6268,22 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-56</v>
+        <v>-53.2</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="125" t="inlineStr">
+      <c r="J51" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6348,7 +6293,7 @@
     <row r="52" ht="64" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -6360,28 +6305,28 @@
         <v>316</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-49.1</v>
+        <v>-51.8</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J52" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
@@ -6389,7 +6334,7 @@
     <row r="53" ht="64" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -6412,15 +6357,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-54.3</v>
+        <v>-55.6</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="125" t="inlineStr">
+      <c r="J53" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6430,7 +6375,7 @@
     <row r="54" ht="64" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6442,28 +6387,18 @@
         <v>316</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="3" t="n">
-        <v>-55.2</v>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J54" s="74" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
@@ -6471,7 +6406,7 @@
     <row r="55" ht="64" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -6487,24 +6422,24 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-51.7</v>
+        <v>-55</v>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J55" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr"/>
@@ -6512,7 +6447,7 @@
     <row r="56" ht="64" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6524,7 +6459,7 @@
         <v>316</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -6535,15 +6470,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-51.2</v>
+        <v>-57.3</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="125" t="inlineStr">
+      <c r="J56" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6553,7 +6488,7 @@
     <row r="57" ht="64" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -6565,28 +6500,28 @@
         <v>316</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-51.6</v>
+        <v>-57.4</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J57" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr"/>
@@ -6594,7 +6529,7 @@
     <row r="58" ht="64" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6606,28 +6541,28 @@
         <v>316</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-54.2</v>
+        <v>-57</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J58" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
@@ -6635,7 +6570,7 @@
     <row r="59" ht="64" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -6649,34 +6584,28 @@
       <c r="D59" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
+      <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="6" t="n">
-        <v>-58</v>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr"/>
+      <c r="J59" s="74" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="64" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6688,28 +6617,28 @@
         <v>316</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>-51.4</v>
+        <v>-56</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J60" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
@@ -6717,7 +6646,7 @@
     <row r="61" ht="64" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -6729,28 +6658,28 @@
         <v>316</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-54.1</v>
+        <v>-55.5</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J61" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr"/>
@@ -6758,7 +6687,7 @@
     <row r="62" ht="64" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -6779,17 +6708,21 @@
       <c r="G62" s="3" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="101" t="inlineStr">
+      <c r="J62" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="64" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -6803,24 +6736,38 @@
       <c r="D63" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F63" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="6" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr"/>
+      <c r="G63" s="6" t="n">
+        <v>-52.2</v>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="101" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr"/>
+      <c r="J63" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="64" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -6834,16 +6781,26 @@
       <c r="D64" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
+      <c r="G64" s="3" t="n">
+        <v>-45.6</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+        </is>
+      </c>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="101" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J64" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
@@ -6851,7 +6808,7 @@
     <row r="65" ht="64" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -6872,7 +6829,7 @@
       <c r="G65" s="6" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="101" t="inlineStr">
+      <c r="J65" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6882,7 +6839,7 @@
     <row r="66" ht="64" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -6903,7 +6860,7 @@
       <c r="G66" s="3" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="101" t="inlineStr">
+      <c r="J66" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6913,7 +6870,7 @@
     <row r="67" ht="64" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -6934,7 +6891,7 @@
       <c r="G67" s="6" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="101" t="inlineStr">
+      <c r="J67" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6944,7 +6901,7 @@
     <row r="68" ht="64" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -6958,16 +6915,26 @@
       <c r="D68" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
+      <c r="G68" s="3" t="n">
+        <v>-53.4</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76</t>
+        </is>
+      </c>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="101" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J68" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
@@ -6975,7 +6942,7 @@
     <row r="69" ht="64" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -6996,7 +6963,7 @@
       <c r="G69" s="6" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="101" t="inlineStr">
+      <c r="J69" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7006,7 +6973,7 @@
     <row r="70" ht="64" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -7027,7 +6994,7 @@
       <c r="G70" s="3" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="101" t="inlineStr">
+      <c r="J70" s="74" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7037,7 +7004,7 @@
     <row r="71" ht="64" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -7051,16 +7018,26 @@
       <c r="D71" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>6E6FD6 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F71" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G71" s="6" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr"/>
+      <c r="G71" s="6" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
       <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="101" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J71" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr"/>
@@ -7068,7 +7045,7 @@
     <row r="72" ht="64" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -7091,29 +7068,25 @@
         <v>0</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>-61.8</v>
+        <v>-51.9</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="125" t="inlineStr">
+      <c r="J72" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K72" s="2" t="inlineStr"/>
     </row>
     <row r="73" ht="64" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -7129,24 +7102,24 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>-60</v>
+        <v>-51.9</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J73" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr"/>
@@ -7154,7 +7127,7 @@
     <row r="74" ht="64" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -7166,28 +7139,28 @@
         <v>175</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>-53.6</v>
+        <v>-52.2</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J74" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
@@ -7195,7 +7168,7 @@
     <row r="75" ht="64" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -7207,28 +7180,28 @@
         <v>175</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>-55.4</v>
+        <v>-52.2</v>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J75" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr"/>
@@ -7236,7 +7209,7 @@
     <row r="76" ht="64" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -7248,28 +7221,28 @@
         <v>175</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>-38.3</v>
+        <v>-42.4</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J76" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
@@ -7277,7 +7250,7 @@
     <row r="77" ht="64" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -7293,24 +7266,24 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F77" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>-52.5</v>
+        <v>-43.3</v>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J77" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr"/>
@@ -7318,7 +7291,7 @@
     <row r="78" ht="64" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -7341,25 +7314,29 @@
         <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>-47.6</v>
+        <v>-46.2</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="125" t="inlineStr">
+      <c r="J78" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="64" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -7375,22 +7352,22 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F79" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>-57.3</v>
+        <v>-45.9</v>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="125" t="inlineStr">
+      <c r="J79" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7400,7 +7377,7 @@
     <row r="80" ht="64" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -7416,24 +7393,24 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>-49.8</v>
+        <v>-53.5</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J80" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
@@ -7441,7 +7418,7 @@
     <row r="81" ht="64" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -7457,14 +7434,14 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F81" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>-41.7</v>
+        <v>-50.2</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
@@ -7472,7 +7449,7 @@
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="125" t="inlineStr">
+      <c r="J81" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7482,7 +7459,7 @@
     <row r="82" ht="64" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -7494,40 +7471,36 @@
         <v>316</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-59</v>
+        <v>-53.4</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="125" t="inlineStr">
+      <c r="J82" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="64" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -7550,7 +7523,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>-58.8</v>
+        <v>-51.1</v>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
@@ -7558,17 +7531,21 @@
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="125" t="inlineStr">
+      <c r="J83" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K83" s="5" t="inlineStr"/>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="64" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -7591,15 +7568,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>-42.2</v>
+        <v>-50.8</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="125" t="inlineStr">
+      <c r="J84" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7613,7 +7590,7 @@
     <row r="85" ht="64" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -7625,7 +7602,7 @@
         <v>316</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
@@ -7636,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>-42.5</v>
+        <v>-50.8</v>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
@@ -7644,17 +7621,21 @@
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="125" t="inlineStr">
+      <c r="J85" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr"/>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="64" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -7666,7 +7647,7 @@
         <v>316</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -7677,15 +7658,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="125" t="inlineStr">
+      <c r="J86" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7695,7 +7676,7 @@
     <row r="87" ht="64" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -7711,14 +7692,14 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F87" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>-47.1</v>
+        <v>-55.1</v>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
@@ -7726,17 +7707,21 @@
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="125" t="inlineStr">
+      <c r="J87" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K87" s="5" t="inlineStr"/>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="64" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -7748,18 +7733,18 @@
         <v>316</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>-37</v>
+        <v>-58.5</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -7767,7 +7752,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="125" t="inlineStr">
+      <c r="J88" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7777,7 +7762,7 @@
     <row r="89" ht="64" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -7789,36 +7774,40 @@
         <v>316</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F89" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>-47.3</v>
+        <v>-58.6</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="125" t="inlineStr">
+      <c r="J89" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr"/>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="64" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -7841,25 +7830,29 @@
         <v>0</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>-46.7</v>
+        <v>-36.3</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="125" t="inlineStr">
+      <c r="J90" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="64" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -7882,7 +7875,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>-41.5</v>
+        <v>-49.1</v>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
@@ -7890,17 +7883,21 @@
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="125" t="inlineStr">
+      <c r="J91" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr"/>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="64" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -7916,24 +7913,24 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-62.3</v>
+        <v>-61.7</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J92" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
@@ -7941,7 +7938,7 @@
     <row r="93" ht="64" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -7964,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>-61.5</v>
+        <v>-62.9</v>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
@@ -7972,7 +7969,7 @@
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="125" t="inlineStr">
+      <c r="J93" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7982,7 +7979,7 @@
     <row r="94" ht="64" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -8005,7 +8002,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>-58.6</v>
+        <v>-53.4</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -8013,7 +8010,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="125" t="inlineStr">
+      <c r="J94" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8023,7 +8020,7 @@
     <row r="95" ht="64" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -8035,28 +8032,28 @@
         <v>30</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F95" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>-57.2</v>
+        <v>-62.4</v>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J95" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr"/>
@@ -8064,7 +8061,7 @@
     <row r="96" ht="64" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -8078,16 +8075,26 @@
       <c r="D96" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F96" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
+      <c r="G96" s="3" t="n">
+        <v>-54.8</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="101" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J96" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
@@ -8095,7 +8102,7 @@
     <row r="97" ht="64" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -8109,24 +8116,38 @@
       <c r="D97" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E97" s="5" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F97" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G97" s="6" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
+      <c r="G97" s="6" t="n">
+        <v>-53.2</v>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="101" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr"/>
+      <c r="J97" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>SCT s0</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="64" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -8149,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-59.1</v>
+        <v>-55.3</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -8157,17 +8178,21 @@
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="115" t="inlineStr">
+      <c r="J98" s="105" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>SCT s01</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="64" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -8179,7 +8204,7 @@
         <v>30</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
@@ -8190,7 +8215,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>-59.6</v>
+        <v>-49.5</v>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
@@ -8198,7 +8223,7 @@
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="125" t="inlineStr">
+      <c r="J99" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8208,7 +8233,7 @@
     <row r="100" ht="64" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -8220,7 +8245,7 @@
         <v>30</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -8231,15 +8256,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-61.2</v>
+        <v>-54.6</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="125" t="inlineStr">
+      <c r="J100" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8249,7 +8274,7 @@
     <row r="101" ht="64" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -8261,36 +8286,40 @@
         <v>30</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0</t>
         </is>
       </c>
       <c r="F101" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>-60.7</v>
+        <v>-51.2</v>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr"/>
+      <c r="J101" s="105" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="64" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -8306,22 +8335,22 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>-56.6</v>
+        <v>-49.9</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="125" t="inlineStr">
+      <c r="J102" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8331,7 +8360,7 @@
     <row r="103" ht="64" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -8347,22 +8376,22 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F103" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>-56.5</v>
+        <v>-50.8</v>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr"/>
-      <c r="J103" s="125" t="inlineStr">
+      <c r="J103" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8372,7 +8401,7 @@
     <row r="104" ht="64" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -8395,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>-57.7</v>
+        <v>-50.9</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -8403,17 +8432,21 @@
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="125" t="inlineStr">
+      <c r="J104" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="64" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -8436,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>-58.1</v>
+        <v>-57.4</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
@@ -8444,7 +8477,7 @@
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr"/>
-      <c r="J105" s="125" t="inlineStr">
+      <c r="J105" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8454,7 +8487,7 @@
     <row r="106" ht="64" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -8477,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-60.4</v>
+        <v>-57.3</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -8485,7 +8518,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="125" t="inlineStr">
+      <c r="J106" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8495,7 +8528,7 @@
     <row r="107" ht="64" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -8507,7 +8540,7 @@
         <v>175</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
@@ -8518,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>-55.2</v>
+        <v>-53.4</v>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
@@ -8526,7 +8559,7 @@
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr"/>
-      <c r="J107" s="125" t="inlineStr">
+      <c r="J107" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8536,7 +8569,7 @@
     <row r="108" ht="64" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -8548,18 +8581,18 @@
         <v>175</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-56.5</v>
+        <v>-50.6</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -8567,7 +8600,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="125" t="inlineStr">
+      <c r="J108" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8577,7 +8610,7 @@
     <row r="109" ht="64" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -8593,14 +8626,14 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F109" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>-53.8</v>
+        <v>-57.2</v>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
@@ -8608,7 +8641,7 @@
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr"/>
-      <c r="J109" s="125" t="inlineStr">
+      <c r="J109" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8618,7 +8651,7 @@
     <row r="110" ht="64" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -8630,26 +8663,26 @@
         <v>175</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>-56.9</v>
+        <v>-57.4</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="125" t="inlineStr">
+      <c r="J110" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8659,7 +8692,7 @@
     <row r="111" ht="64" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -8671,28 +8704,28 @@
         <v>175</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F111" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>-56</v>
+        <v>-50</v>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr"/>
-      <c r="J111" s="115" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J111" s="124" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr"/>
@@ -8700,7 +8733,7 @@
     <row r="112" ht="64" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -8712,26 +8745,26 @@
         <v>316</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-54.8</v>
+        <v>-48.9</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="125" t="inlineStr">
+      <c r="J112" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8741,7 +8774,7 @@
     <row r="113" ht="64" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -8753,26 +8786,26 @@
         <v>316</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>-67.2</v>
+        <v>-49.1</v>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="125" t="inlineStr">
+      <c r="J113" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8782,7 +8815,7 @@
     <row r="114" ht="64" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -8805,7 +8838,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>-66.2</v>
+        <v>-56.1</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -8813,7 +8846,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="125" t="inlineStr">
+      <c r="J114" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8823,7 +8856,7 @@
     <row r="115" ht="64" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -8835,7 +8868,7 @@
         <v>316</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
@@ -8846,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>-53.9</v>
+        <v>-56.3</v>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
@@ -8854,7 +8887,7 @@
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr"/>
-      <c r="J115" s="125" t="inlineStr">
+      <c r="J115" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8864,7 +8897,7 @@
     <row r="116" ht="64" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -8876,26 +8909,26 @@
         <v>316</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>-54.2</v>
+        <v>-57.9</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="125" t="inlineStr">
+      <c r="J116" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8905,7 +8938,7 @@
     <row r="117" ht="64" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -8921,22 +8954,22 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F117" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>-53.8</v>
+        <v>-53.7</v>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr"/>
-      <c r="J117" s="125" t="inlineStr">
+      <c r="J117" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8946,7 +8979,7 @@
     <row r="118" ht="64" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -8958,7 +8991,7 @@
         <v>316</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
@@ -8969,7 +9002,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>-53.9</v>
+        <v>-48.8</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -8977,7 +9010,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="125" t="inlineStr">
+      <c r="J118" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8987,7 +9020,7 @@
     <row r="119" ht="64" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -9003,22 +9036,22 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F119" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>-54.2</v>
+        <v>-51.7</v>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr"/>
-      <c r="J119" s="125" t="inlineStr">
+      <c r="J119" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9028,7 +9061,7 @@
     <row r="120" ht="64" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -9040,7 +9073,7 @@
         <v>316</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
@@ -9051,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>-54.1</v>
+        <v>-55.9</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -9059,7 +9092,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="125" t="inlineStr">
+      <c r="J120" s="124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9069,7 +9102,7 @@
     <row r="121" ht="64" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>20260528-124145</t>
+          <t>20260528-151034</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -9092,7 +9125,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>-54.1</v>
+        <v>-56.8</v>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
@@ -9106,51 +9139,6 @@
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr"/>
-    </row>
-    <row r="122" ht="64" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>20260528-124145</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_half_full_cup_empty</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>-54.8</v>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="126" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>these test runs were done with an metal fin in the middle</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/beer-pour-results.xlsx
+++ b/beer-pour-results.xlsx
@@ -39,7 +39,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00065F46"/>
       <sz val="11"/>
     </font>
     <font>
@@ -51,7 +51,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
+      <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -76,8 +76,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,8 +94,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +144,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -156,30 +159,297 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -189,64 +459,31 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -255,247 +492,13 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3923,6 +3926,34 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId120"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>121</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="121" name="Image 121" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4225,7 +4256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4301,7 +4332,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -4310,21 +4341,31 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="G2" s="3" t="n">
+        <v>-52.7</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J2" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -4332,7 +4373,7 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4341,21 +4382,31 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E3" s="5" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
+      <c r="G3" s="6" t="n">
+        <v>-54.5</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J3" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr"/>
@@ -4363,7 +4414,7 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4372,31 +4423,31 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-55.6</v>
+        <v>-51.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J4" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -4404,7 +4455,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4413,21 +4464,31 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E5" s="5" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="n">
+        <v>-50.6</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J5" s="124" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr"/>
@@ -4435,7 +4496,7 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -4444,33 +4505,39 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="G6" s="3" t="n">
+        <v>-57.5</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="J6" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4479,33 +4546,39 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
+        <v>-53.6</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="J7" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4514,21 +4587,31 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="G8" s="3" t="n">
+        <v>-50.5</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J8" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -4536,7 +4619,7 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -4545,21 +4628,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>-50.6</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J9" s="124" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr"/>
@@ -4567,7 +4660,7 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4576,21 +4669,31 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="G10" s="3" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J10" s="124" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -4598,7 +4701,7 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -4607,21 +4710,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="G11" s="6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J11" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr"/>
@@ -4629,7 +4742,7 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4638,43 +4751,29 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>-49.6</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
-        </is>
-      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="124" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="J12" s="117" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -4683,43 +4782,39 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-53.7</v>
+        <v>-54.6</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="124" t="inlineStr">
+      <c r="J13" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="64" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4728,43 +4823,39 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-51.5</v>
+        <v>-55.7</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -4773,29 +4864,29 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-52.2</v>
+        <v>-50.7</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="124" t="inlineStr">
+      <c r="J15" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4805,7 +4896,7 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -4814,31 +4905,31 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-51.9</v>
+        <v>-58.3</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -4846,7 +4937,7 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -4855,29 +4946,29 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-48.7</v>
+        <v>-54.5</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="124" t="inlineStr">
+      <c r="J17" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4887,7 +4978,7 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -4896,29 +4987,29 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-48.2</v>
+        <v>-56.1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="105" t="inlineStr">
+      <c r="J18" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -4928,7 +5019,7 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -4937,29 +5028,29 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-50.3</v>
+        <v>-53.3</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="124" t="inlineStr">
+      <c r="J19" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4969,7 +5060,7 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -4978,29 +5069,29 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-47</v>
+        <v>-53.9</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="124" t="inlineStr">
+      <c r="J20" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5010,7 +5101,7 @@
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -5019,29 +5110,29 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-51.4</v>
+        <v>-59.3</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="124" t="inlineStr">
+      <c r="J21" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5051,7 +5142,7 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -5063,26 +5154,26 @@
         <v>316</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-57.5</v>
+        <v>-50.4</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="124" t="inlineStr">
+      <c r="J22" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5092,7 +5183,7 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -5104,26 +5195,26 @@
         <v>316</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-46.4</v>
+        <v>-54.1</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="124" t="inlineStr">
+      <c r="J23" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5133,7 +5224,7 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -5145,26 +5236,26 @@
         <v>316</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-47.8</v>
+        <v>-50.6</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="124" t="inlineStr">
+      <c r="J24" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5174,7 +5265,7 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -5186,26 +5277,26 @@
         <v>316</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-45.2</v>
+        <v>-50.5</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="124" t="inlineStr">
+      <c r="J25" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5215,7 +5306,7 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5227,26 +5318,26 @@
         <v>316</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-53.6</v>
+        <v>-50.9</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="124" t="inlineStr">
+      <c r="J26" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5256,7 +5347,7 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -5268,28 +5359,28 @@
         <v>316</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-48.5</v>
+        <v>-50.4</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr"/>
@@ -5297,7 +5388,7 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -5309,28 +5400,28 @@
         <v>316</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-53.2</v>
+        <v>-50.9</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -5338,7 +5429,7 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -5350,26 +5441,26 @@
         <v>316</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-53.7</v>
+        <v>-55</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="124" t="inlineStr">
+      <c r="J29" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5379,7 +5470,7 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -5391,28 +5482,28 @@
         <v>316</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-46.1</v>
+        <v>-55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
@@ -5420,7 +5511,7 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -5432,28 +5523,28 @@
         <v>316</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-50</v>
+        <v>-54.8</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr"/>
@@ -5461,7 +5552,7 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -5470,31 +5561,31 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>-60.7</v>
+        <v>-54.8</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
@@ -5502,7 +5593,7 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -5511,10 +5602,10 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -5525,7 +5616,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-60.6</v>
+        <v>-57</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
@@ -5533,7 +5624,7 @@
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="124" t="inlineStr">
+      <c r="J33" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5543,7 +5634,7 @@
     <row r="34" ht="64" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -5552,31 +5643,31 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>-54.1</v>
+        <v>-54.4</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
@@ -5584,7 +5675,7 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -5593,10 +5684,10 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -5607,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-54.9</v>
+        <v>-54.8</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -5615,7 +5706,7 @@
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="124" t="inlineStr">
+      <c r="J35" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5625,7 +5716,7 @@
     <row r="36" ht="64" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -5634,29 +5725,29 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-56.2</v>
+        <v>-50.9</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="124" t="inlineStr">
+      <c r="J36" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5666,7 +5757,7 @@
     <row r="37" ht="64" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -5675,31 +5766,31 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-58.9</v>
+        <v>-50.9</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr"/>
@@ -5707,7 +5798,7 @@
     <row r="38" ht="64" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5716,10 +5807,10 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -5730,7 +5821,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>-57.8</v>
+        <v>-54.6</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -5738,7 +5829,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="124" t="inlineStr">
+      <c r="J38" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5748,7 +5839,7 @@
     <row r="39" ht="64" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -5757,31 +5848,21 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="6" t="n">
-        <v>-58.3</v>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
+      <c r="G39" s="6" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J39" s="117" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr"/>
@@ -5789,7 +5870,7 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -5798,31 +5879,31 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-58</v>
+        <v>-54.5</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J40" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
@@ -5830,7 +5911,7 @@
     <row r="41" ht="64" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -5839,31 +5920,31 @@
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-59.1</v>
+        <v>-50.3</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr"/>
@@ -5871,7 +5952,7 @@
     <row r="42" ht="64" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -5880,43 +5961,39 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>60</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>-54.4</v>
+        <v>-54.8</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="J42" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="64" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -5925,43 +6002,39 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-54.2</v>
+        <v>-50.9</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="105" t="inlineStr">
+      <c r="J43" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K43" s="5" t="inlineStr"/>
     </row>
     <row r="44" ht="64" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -5970,43 +6043,39 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>-53.3</v>
+        <v>-55.5</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="124" t="inlineStr">
+      <c r="J44" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="64" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -6015,31 +6084,31 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-51</v>
+        <v>-52.8</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr"/>
@@ -6047,7 +6116,7 @@
     <row r="46" ht="64" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6056,29 +6125,29 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-53.5</v>
+        <v>-52.5</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="105" t="inlineStr">
+      <c r="J46" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -6088,7 +6157,7 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -6097,31 +6166,31 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-56.8</v>
+        <v>-54.9</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr"/>
@@ -6129,7 +6198,7 @@
     <row r="48" ht="64" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6138,31 +6207,31 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>-57.2</v>
+        <v>-52.1</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J48" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
@@ -6170,7 +6239,7 @@
     <row r="49" ht="64" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -6179,21 +6248,21 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>62</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-57.5</v>
+        <v>-52.2</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
@@ -6201,7 +6270,7 @@
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="105" t="inlineStr">
+      <c r="J49" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -6211,7 +6280,7 @@
     <row r="50" ht="64" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -6220,31 +6289,21 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="3" t="n">
-        <v>-59.3</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="124" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J50" s="117" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
@@ -6252,7 +6311,7 @@
     <row r="51" ht="64" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -6261,10 +6320,10 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
@@ -6275,15 +6334,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-53.2</v>
+        <v>-53.8</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="124" t="inlineStr">
+      <c r="J51" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6293,7 +6352,7 @@
     <row r="52" ht="64" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -6305,7 +6364,7 @@
         <v>316</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -6316,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-51.8</v>
+        <v>-56.6</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -6324,7 +6383,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="105" t="inlineStr">
+      <c r="J52" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -6334,7 +6393,7 @@
     <row r="53" ht="64" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -6346,28 +6405,28 @@
         <v>316</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-55.6</v>
+        <v>-49.4</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr"/>
@@ -6375,7 +6434,7 @@
     <row r="54" ht="64" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6387,18 +6446,28 @@
         <v>316</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="G54" s="3" t="n">
+        <v>-55.1</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J54" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
@@ -6406,7 +6475,7 @@
     <row r="55" ht="64" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -6418,28 +6487,28 @@
         <v>316</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-55</v>
+        <v>-54.1</v>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J55" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr"/>
@@ -6447,7 +6516,7 @@
     <row r="56" ht="64" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6459,26 +6528,26 @@
         <v>316</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-57.3</v>
+        <v>-57</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="124" t="inlineStr">
+      <c r="J56" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6488,7 +6557,7 @@
     <row r="57" ht="64" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -6500,26 +6569,26 @@
         <v>316</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-57.4</v>
+        <v>-50.3</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="105" t="inlineStr">
+      <c r="J57" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -6529,7 +6598,7 @@
     <row r="58" ht="64" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6541,28 +6610,28 @@
         <v>316</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-57</v>
+        <v>-51.9</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J58" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
@@ -6570,7 +6639,7 @@
     <row r="59" ht="64" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -6582,30 +6651,36 @@
         <v>316</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E59" s="5" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="6" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
+      <c r="G59" s="6" t="n">
+        <v>-55.9</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
+      <c r="J59" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="64" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6617,28 +6692,28 @@
         <v>316</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>-56</v>
+        <v>-53.8</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J60" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
@@ -6646,7 +6721,7 @@
     <row r="61" ht="64" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -6658,26 +6733,26 @@
         <v>316</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-55.5</v>
+        <v>-54.4</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="124" t="inlineStr">
+      <c r="J61" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6687,118 +6762,120 @@
     <row r="62" ht="64" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F62" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
+      <c r="G62" s="3" t="n">
+        <v>-56.3</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="J62" s="124" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63" ht="64" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>-52.2</v>
+        <v>-55.7</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="J63" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr"/>
     </row>
     <row r="64" ht="64" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>-45.6</v>
+        <v>-53</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="124" t="inlineStr">
+      <c r="J64" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6808,30 +6885,40 @@
     <row r="65" ht="64" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E65" s="5" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F65" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="6" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr"/>
+      <c r="G65" s="6" t="n">
+        <v>-51.2</v>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J65" s="124" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr"/>
@@ -6839,30 +6926,40 @@
     <row r="66" ht="64" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
+      <c r="G66" s="3" t="n">
+        <v>-58.5</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+        </is>
+      </c>
       <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J66" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
@@ -6870,30 +6967,40 @@
     <row r="67" ht="64" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E67" s="5" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="6" t="inlineStr"/>
-      <c r="H67" s="5" t="inlineStr"/>
+      <c r="G67" s="6" t="n">
+        <v>-56.4</v>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J67" s="124" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr"/>
@@ -6901,38 +7008,38 @@
     <row r="68" ht="64" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>-53.4</v>
+        <v>-49</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="105" t="inlineStr">
+      <c r="J68" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -6942,30 +7049,40 @@
     <row r="69" ht="64" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="E69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F69" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G69" s="6" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr"/>
+      <c r="G69" s="6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J69" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr"/>
@@ -6973,30 +7090,40 @@
     <row r="70" ht="64" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+        </is>
+      </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="G70" s="3" t="n">
+        <v>-51.8</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="74" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J70" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
@@ -7004,40 +7131,40 @@
     <row r="71" ht="64" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D71" s="6" t="n">
         <v>66</v>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F71" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>-48</v>
+        <v>-55.8</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J71" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr"/>
@@ -7045,38 +7172,38 @@
     <row r="72" ht="64" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>-51.9</v>
+        <v>-55.9</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="124" t="inlineStr">
+      <c r="J72" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7086,38 +7213,38 @@
     <row r="73" ht="64" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>-51.9</v>
+        <v>-53.8</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="124" t="inlineStr">
+      <c r="J73" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7127,38 +7254,38 @@
     <row r="74" ht="64" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>-52.2</v>
+        <v>-54.2</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="124" t="inlineStr">
+      <c r="J74" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7168,40 +7295,40 @@
     <row r="75" ht="64" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>-52.2</v>
+        <v>-45.1</v>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr"/>
@@ -7209,38 +7336,38 @@
     <row r="76" ht="64" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>-42.4</v>
+        <v>-55.8</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="124" t="inlineStr">
+      <c r="J76" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7250,38 +7377,38 @@
     <row r="77" ht="64" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F77" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>-43.3</v>
+        <v>-57.1</v>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="124" t="inlineStr">
+      <c r="J77" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7291,83 +7418,79 @@
     <row r="78" ht="64" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>-46.2</v>
+        <v>-54.5</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
     </row>
     <row r="79" ht="64" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F79" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>-45.9</v>
+        <v>-54.7</v>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="124" t="inlineStr">
+      <c r="J79" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7377,38 +7500,38 @@
     <row r="80" ht="64" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>-53.5</v>
+        <v>-53.2</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="124" t="inlineStr">
+      <c r="J80" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7418,38 +7541,38 @@
     <row r="81" ht="64" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C81" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F81" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>-50.2</v>
+        <v>-53.5</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="124" t="inlineStr">
+      <c r="J81" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7459,38 +7582,38 @@
     <row r="82" ht="64" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-53.4</v>
+        <v>-56.1</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="124" t="inlineStr">
+      <c r="J82" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7500,175 +7623,163 @@
     <row r="83" ht="64" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C83" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F83" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>-51.1</v>
+        <v>-55.1</v>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="124" t="inlineStr">
+      <c r="J83" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K83" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K83" s="5" t="inlineStr"/>
     </row>
     <row r="84" ht="64" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>-50.8</v>
+        <v>-55</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="64" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C85" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F85" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>-50.8</v>
+        <v>-53.4</v>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="124" t="inlineStr">
+      <c r="J85" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K85" s="5" t="inlineStr"/>
     </row>
     <row r="86" ht="64" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>-54</v>
+        <v>-51.6</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
@@ -7676,85 +7787,61 @@
     <row r="87" ht="64" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C87" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="E87" s="5" t="inlineStr"/>
       <c r="F87" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="6" t="n">
-        <v>-55.1</v>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
-        </is>
-      </c>
+      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="5" t="inlineStr"/>
       <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="124" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="J87" s="117" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr"/>
     </row>
     <row r="88" ht="64" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="3" t="n">
-        <v>-58.5</v>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
-        </is>
-      </c>
+      <c r="G88" s="3" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="124" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J88" s="117" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
@@ -7762,154 +7849,142 @@
     <row r="89" ht="64" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C89" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F89" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>-58.6</v>
+        <v>-53.5</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="124" t="inlineStr">
+      <c r="J89" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K89" s="5" t="inlineStr"/>
     </row>
     <row r="90" ht="64" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>-36.3</v>
+        <v>-51.1</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="64" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C91" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F91" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>-49.1</v>
+        <v>-53</v>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="124" t="inlineStr">
+      <c r="J91" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="K91" s="5" t="inlineStr"/>
     </row>
     <row r="92" ht="64" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -7920,7 +7995,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-61.7</v>
+        <v>-56.3</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -7928,7 +8003,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="105" t="inlineStr">
+      <c r="J92" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -7938,38 +8013,38 @@
     <row r="93" ht="64" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>-62.9</v>
+        <v>-53.8</v>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="124" t="inlineStr">
+      <c r="J93" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7979,38 +8054,38 @@
     <row r="94" ht="64" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>-53.4</v>
+        <v>-55.4</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="124" t="inlineStr">
+      <c r="J94" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8020,30 +8095,30 @@
     <row r="95" ht="64" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C95" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F95" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>-62.4</v>
+        <v>-50.9</v>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
@@ -8051,7 +8126,7 @@
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="105" t="inlineStr">
+      <c r="J95" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -8061,38 +8136,38 @@
     <row r="96" ht="64" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>-54.8</v>
+        <v>-53.9</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="124" t="inlineStr">
+      <c r="J96" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8102,109 +8177,101 @@
     <row r="97" ht="64" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F97" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>-53.2</v>
+        <v>-53.7</v>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t>SCT s0</t>
-        </is>
-      </c>
+      <c r="J97" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr"/>
     </row>
     <row r="98" ht="64" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-55.3</v>
+        <v>-54.4</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="105" t="inlineStr">
+      <c r="J98" s="124" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>SCT s01</t>
-        </is>
-      </c>
+      <c r="K98" s="2" t="inlineStr"/>
     </row>
     <row r="99" ht="64" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
@@ -8215,15 +8282,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>-49.5</v>
+        <v>-54.1</v>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="124" t="inlineStr">
+      <c r="J99" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8233,19 +8300,19 @@
     <row r="100" ht="64" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -8256,15 +8323,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-54.6</v>
+        <v>-52.7</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="124" t="inlineStr">
+      <c r="J100" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8274,85 +8341,81 @@
     <row r="101" ht="64" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C101" s="6" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F101" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>-51.2</v>
+        <v>-55.7</v>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="105" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
+      <c r="J101" s="125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="64" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>-49.9</v>
+        <v>-51.2</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
@@ -8360,40 +8423,40 @@
     <row r="103" ht="64" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C103" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F103" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>-50.8</v>
+        <v>-55.5</v>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr"/>
       <c r="J103" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr"/>
@@ -8401,85 +8464,81 @@
     <row r="104" ht="64" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>-50.9</v>
+        <v>-52.8</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
     </row>
     <row r="105" ht="64" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F105" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>-57.4</v>
+        <v>-49.4</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr"/>
       <c r="J105" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr"/>
@@ -8487,40 +8546,30 @@
     <row r="106" ht="64" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G106" s="3" t="n">
-        <v>-57.3</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
+      <c r="G106" s="3" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="124" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J106" s="117" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
@@ -8528,40 +8577,30 @@
     <row r="107" ht="64" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C107" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G107" s="6" t="n">
-        <v>-53.4</v>
-      </c>
-      <c r="H107" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr"/>
-      <c r="J107" s="124" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J107" s="117" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr"/>
@@ -8569,40 +8608,40 @@
     <row r="108" ht="64" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>62</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-50.6</v>
+        <v>-55.4</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
@@ -8610,19 +8649,19 @@
     <row r="109" ht="64" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C109" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
@@ -8633,15 +8672,15 @@
         <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>-57.2</v>
+        <v>-54</v>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr"/>
-      <c r="J109" s="124" t="inlineStr">
+      <c r="J109" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8651,16 +8690,16 @@
     <row r="110" ht="64" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>62</v>
@@ -8674,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>-57.4</v>
+        <v>-50.3</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -8682,7 +8721,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="124" t="inlineStr">
+      <c r="J110" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8692,40 +8731,30 @@
     <row r="111" ht="64" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C111" s="6" t="n">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G111" s="6" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
+      <c r="G111" s="6" t="inlineStr"/>
+      <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr"/>
-      <c r="J111" s="124" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J111" s="117" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr"/>
@@ -8733,94 +8762,92 @@
     <row r="112" ht="64" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-48.9</v>
+        <v>-56.3</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr"/>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="64" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C113" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G113" s="6" t="n">
-        <v>-49.1</v>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
+      <c r="G113" s="6" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="124" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr"/>
+      <c r="J113" s="117" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="64" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -8838,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>-56.1</v>
+        <v>-51.9</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -8846,29 +8873,33 @@
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="124" t="inlineStr">
+      <c r="J114" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="64" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C115" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
@@ -8879,7 +8910,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>-56.3</v>
+        <v>-54.2</v>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
@@ -8887,7 +8918,7 @@
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr"/>
-      <c r="J115" s="124" t="inlineStr">
+      <c r="J115" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8897,19 +8928,19 @@
     <row r="116" ht="64" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -8920,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>-57.9</v>
+        <v>-54.2</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -8928,7 +8959,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="124" t="inlineStr">
+      <c r="J116" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8938,19 +8969,19 @@
     <row r="117" ht="64" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C117" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
@@ -8961,15 +8992,15 @@
         <v>0</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>-53.7</v>
+        <v>-50.6</v>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr"/>
-      <c r="J117" s="124" t="inlineStr">
+      <c r="J117" s="125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8979,40 +9010,40 @@
     <row r="118" ht="64" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>-48.8</v>
+        <v>-60</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
@@ -9020,40 +9051,40 @@
     <row r="119" ht="64" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C119" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F119" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>-51.7</v>
+        <v>-53.4</v>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr"/>
       <c r="J119" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr"/>
@@ -9061,40 +9092,40 @@
     <row r="120" ht="64" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>-55.9</v>
+        <v>-51.1</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="124" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
@@ -9102,19 +9133,19 @@
     <row r="121" ht="64" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>20260528-151034</t>
+          <t>20260528-164756</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_half_full_cup_empty</t>
+          <t>drip_tray_empty_cup_empty</t>
         </is>
       </c>
       <c r="C121" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
@@ -9125,7 +9156,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>-56.8</v>
+        <v>-56.3</v>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
@@ -9139,6 +9170,47 @@
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122" ht="64" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>20260528-164756</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>drip_tray_empty_cup_empty</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>E73842 -&gt; ant0</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73842</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="126" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/beer-pour-results.xlsx
+++ b/beer-pour-results.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,14 +48,8 @@
       <color rgb="0092400E"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00991B1B"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -92,12 +86,6 @@
         <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -121,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,28 +135,85 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -180,12 +225,66 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -213,292 +312,58 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2806,1154 +2671,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>81</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="82" name="Image 82" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>83</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="83" name="Image 83" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>84</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="84" name="Image 84" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>85</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>87</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>90</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="91" name="Image 91" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="92" name="Image 92" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>93</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="93" name="Image 93" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>95</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>96</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>98</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="98" name="Image 98" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>99</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="99" name="Image 99" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="100" name="Image 100" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>101</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="101" name="Image 101" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="102" name="Image 102" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>103</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="103" name="Image 103" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="104" name="Image 104" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>105</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="105" name="Image 105" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>106</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="106" name="Image 106" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>107</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="107" name="Image 107" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="108" name="Image 108" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="109" name="Image 109" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId109"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>110</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="110" name="Image 110" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId110"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>111</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="111" name="Image 111" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId111"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="112" name="Image 112" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId112"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>113</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="113" name="Image 113" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId113"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="114" name="Image 114" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId114"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="115" name="Image 115" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId115"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>116</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="116" name="Image 116" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId116"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>117</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="117" name="Image 117" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId117"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="118" name="Image 118" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId118"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>119</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="119" name="Image 119" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId119"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>120</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="120" name="Image 120" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId120"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>121</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1019175" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="121" name="Image 121" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4256,7 +2973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4332,7 +3049,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -4344,26 +3061,26 @@
         <v>316</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-52.7</v>
+        <v>-47.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="125" t="inlineStr">
+      <c r="J2" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4373,7 +3090,7 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4385,26 +3102,26 @@
         <v>316</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-54.5</v>
+        <v>-49.9</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="125" t="inlineStr">
+      <c r="J3" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4414,7 +3131,7 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4426,26 +3143,26 @@
         <v>316</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-51.8</v>
+        <v>-47</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="125" t="inlineStr">
+      <c r="J4" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4455,7 +3172,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4467,28 +3184,28 @@
         <v>316</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-50.6</v>
+        <v>-41.2</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J5" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr"/>
@@ -4496,7 +3213,7 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -4512,24 +3229,24 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-57.5</v>
+        <v>-49.7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J6" s="59" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -4537,7 +3254,7 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4549,26 +3266,26 @@
         <v>316</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-53.6</v>
+        <v>-42.6</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="125" t="inlineStr">
+      <c r="J7" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4578,7 +3295,7 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4590,28 +3307,28 @@
         <v>316</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-50.5</v>
+        <v>-48.9</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J8" s="59" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -4619,7 +3336,7 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -4631,28 +3348,28 @@
         <v>316</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-50.6</v>
+        <v>-49.9</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J9" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr"/>
@@ -4660,7 +3377,7 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4672,28 +3389,28 @@
         <v>316</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-52.5</v>
+        <v>-45.3</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J10" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -4701,7 +3418,7 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -4713,26 +3430,26 @@
         <v>316</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-55</v>
+        <v>-42.3</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="125" t="inlineStr">
+      <c r="J11" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4742,7 +3459,7 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4754,18 +3471,28 @@
         <v>316</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="G12" s="3" t="n">
+        <v>-50.2</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="117" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J12" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -4773,7 +3500,7 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -4785,26 +3512,26 @@
         <v>316</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-54.6</v>
+        <v>-45.1</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="125" t="inlineStr">
+      <c r="J13" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4814,7 +3541,7 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4826,28 +3553,28 @@
         <v>316</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-55.7</v>
+        <v>-45.8</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J14" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
@@ -4855,7 +3582,7 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -4867,26 +3594,26 @@
         <v>316</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-50.7</v>
+        <v>-45.5</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="125" t="inlineStr">
+      <c r="J15" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4896,7 +3623,7 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -4908,28 +3635,28 @@
         <v>316</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-58.3</v>
+        <v>-44.8</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J16" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -4937,7 +3664,7 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -4949,26 +3676,26 @@
         <v>316</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-54.5</v>
+        <v>-53.3</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="125" t="inlineStr">
+      <c r="J17" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4978,7 +3705,7 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -4990,28 +3717,28 @@
         <v>316</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-56.1</v>
+        <v>-48.2</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J18" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -5019,7 +3746,7 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -5031,26 +3758,26 @@
         <v>316</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-53.3</v>
+        <v>-43.9</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="125" t="inlineStr">
+      <c r="J19" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5060,7 +3787,7 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -5072,26 +3799,26 @@
         <v>316</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-53.9</v>
+        <v>-45.9</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="125" t="inlineStr">
+      <c r="J20" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5101,7 +3828,7 @@
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -5117,22 +3844,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-59.3</v>
+        <v>-50.4</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="125" t="inlineStr">
+      <c r="J21" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5142,7 +3869,7 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -5154,28 +3881,28 @@
         <v>316</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-50.4</v>
+        <v>-50.9</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J22" s="59" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
@@ -5183,7 +3910,7 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -5195,7 +3922,7 @@
         <v>316</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -5206,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-54.1</v>
+        <v>-55.8</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -5214,7 +3941,7 @@
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="125" t="inlineStr">
+      <c r="J23" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5224,7 +3951,7 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -5236,18 +3963,18 @@
         <v>316</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-50.6</v>
+        <v>-52.1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -5255,7 +3982,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="125" t="inlineStr">
+      <c r="J24" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5265,7 +3992,7 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -5277,7 +4004,7 @@
         <v>316</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -5288,15 +4015,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-50.5</v>
+        <v>-53.1</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="125" t="inlineStr">
+      <c r="J25" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5306,7 +4033,7 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5318,26 +4045,26 @@
         <v>316</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-50.9</v>
+        <v>-51.4</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="125" t="inlineStr">
+      <c r="J26" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5347,7 +4074,7 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -5359,28 +4086,28 @@
         <v>316</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-50.4</v>
+        <v>-54.7</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J27" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr"/>
@@ -5388,7 +4115,7 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -5400,28 +4127,28 @@
         <v>316</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-50.9</v>
+        <v>-52.6</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J28" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -5429,7 +4156,7 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -5441,7 +4168,7 @@
         <v>316</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -5452,15 +4179,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-55</v>
+        <v>-55.9</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="125" t="inlineStr">
+      <c r="J29" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5470,7 +4197,7 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -5482,28 +4209,28 @@
         <v>316</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-55</v>
+        <v>-51.4</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J30" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
@@ -5511,7 +4238,7 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -5523,28 +4250,28 @@
         <v>316</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-54.8</v>
+        <v>-61.4</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J31" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr"/>
@@ -5552,7 +4279,7 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -5564,28 +4291,28 @@
         <v>316</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>-54.8</v>
+        <v>-50.1</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J32" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
@@ -5593,7 +4320,7 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -5609,24 +4336,24 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-57</v>
+        <v>-49.7</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J33" s="59" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr"/>
@@ -5634,7 +4361,7 @@
     <row r="34" ht="64" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -5650,24 +4377,24 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>-54.4</v>
+        <v>-48.8</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J34" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
@@ -5675,7 +4402,7 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -5687,26 +4414,26 @@
         <v>316</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-54.8</v>
+        <v>-50.8</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="125" t="inlineStr">
+      <c r="J35" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5716,7 +4443,7 @@
     <row r="36" ht="64" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -5732,14 +4459,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-50.9</v>
+        <v>-53</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -5747,7 +4474,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="125" t="inlineStr">
+      <c r="J36" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5757,7 +4484,7 @@
     <row r="37" ht="64" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -5769,28 +4496,28 @@
         <v>316</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-50.9</v>
+        <v>-52.1</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J37" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr"/>
@@ -5798,7 +4525,7 @@
     <row r="38" ht="64" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5810,7 +4537,7 @@
         <v>316</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -5821,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>-54.6</v>
+        <v>-57</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -5829,7 +4556,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="125" t="inlineStr">
+      <c r="J38" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5839,7 +4566,7 @@
     <row r="39" ht="64" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -5853,16 +4580,26 @@
       <c r="D39" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="E39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr"/>
+      <c r="G39" s="6" t="n">
+        <v>-53.9</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+        </is>
+      </c>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="117" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J39" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr"/>
@@ -5870,7 +4607,7 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -5893,15 +4630,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-54.5</v>
+        <v>-51.4</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="125" t="inlineStr">
+      <c r="J40" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5911,7 +4648,7 @@
     <row r="41" ht="64" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -5923,11 +4660,11 @@
         <v>316</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
@@ -5938,13 +4675,13 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J41" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr"/>
@@ -5952,38 +4689,38 @@
     <row r="42" ht="64" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>-54.8</v>
+        <v>-57.4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="125" t="inlineStr">
+      <c r="J42" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5993,40 +4730,40 @@
     <row r="43" ht="64" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-50.9</v>
+        <v>-58.2</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J43" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr"/>
@@ -6034,38 +4771,38 @@
     <row r="44" ht="64" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>-55.5</v>
+        <v>-58.4</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="125" t="inlineStr">
+      <c r="J44" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6075,40 +4812,40 @@
     <row r="45" ht="64" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-52.8</v>
+        <v>-44.9</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J45" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr"/>
@@ -6116,40 +4853,40 @@
     <row r="46" ht="64" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-52.5</v>
+        <v>-55.4</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J46" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -6157,40 +4894,40 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-54.9</v>
+        <v>-50.2</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J47" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr"/>
@@ -6198,38 +4935,38 @@
     <row r="48" ht="64" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>-52.1</v>
+        <v>-47.1</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="125" t="inlineStr">
+      <c r="J48" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6239,38 +4976,38 @@
     <row r="49" ht="64" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-52.2</v>
+        <v>-42.4</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="124" t="inlineStr">
+      <c r="J49" s="59" t="inlineStr">
         <is>
           <t>LOPSIDED</t>
         </is>
@@ -6280,30 +5017,40 @@
     <row r="50" ht="64" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
+        </is>
+      </c>
       <c r="F50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="G50" s="3" t="n">
+        <v>-51.8</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
+        </is>
+      </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="117" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J50" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
@@ -6311,38 +5058,38 @@
     <row r="51" ht="64" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-53.8</v>
+        <v>-62.1</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="125" t="inlineStr">
+      <c r="J51" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6352,40 +5099,40 @@
     <row r="52" ht="64" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-56.6</v>
+        <v>-49</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J52" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
@@ -6393,40 +5140,40 @@
     <row r="53" ht="64" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-49.4</v>
+        <v>-36.2</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J53" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr"/>
@@ -6434,38 +5181,38 @@
     <row r="54" ht="64" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>-55.1</v>
+        <v>-42.9</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="125" t="inlineStr">
+      <c r="J54" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6475,40 +5222,40 @@
     <row r="55" ht="64" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-54.1</v>
+        <v>-45.9</v>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J55" s="59" t="inlineStr">
+        <is>
+          <t>LOPSIDED</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr"/>
@@ -6516,38 +5263,38 @@
     <row r="56" ht="64" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-57</v>
+        <v>-47.7</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="125" t="inlineStr">
+      <c r="J56" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6557,40 +5304,40 @@
     <row r="57" ht="64" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-50.3</v>
+        <v>-43.1</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J57" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr"/>
@@ -6598,38 +5345,38 @@
     <row r="58" ht="64" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant1, 6E6FD6 -&gt; ant0</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-51.9</v>
+        <v>-54.1</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="125" t="inlineStr">
+      <c r="J58" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6639,38 +5386,38 @@
     <row r="59" ht="64" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-55.9</v>
+        <v>-49.1</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6FD6, E2801191A5040076596E6F76</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="125" t="inlineStr">
+      <c r="J59" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6680,38 +5427,38 @@
     <row r="60" ht="64" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>-53.8</v>
+        <v>-50.9</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="125" t="inlineStr">
+      <c r="J60" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6721,38 +5468,38 @@
     <row r="61" ht="64" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>6E6F76 -&gt; ant0, 6E6FD6 -&gt; ant1</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-54.4</v>
+        <v>-50.2</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E2801191A5040076596E6F76, E2801191A5040076596E6FD6</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="125" t="inlineStr">
+      <c r="J61" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6762,40 +5509,40 @@
     <row r="62" ht="64" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-56.3</v>
+        <v>-58.7</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J62" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
@@ -6803,38 +5550,38 @@
     <row r="63" ht="64" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>-55.7</v>
+        <v>-53.6</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="125" t="inlineStr">
+      <c r="J63" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6844,19 +5591,19 @@
     <row r="64" ht="64" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -6867,15 +5614,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>-53</v>
+        <v>-51.1</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="125" t="inlineStr">
+      <c r="J64" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6885,40 +5632,40 @@
     <row r="65" ht="64" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F65" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>-51.2</v>
+        <v>-47.4</v>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J65" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr"/>
@@ -6926,38 +5673,38 @@
     <row r="66" ht="64" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>-58.5</v>
+        <v>-55.1</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="125" t="inlineStr">
+      <c r="J66" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6967,40 +5714,40 @@
     <row r="67" ht="64" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F67" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>-56.4</v>
+        <v>-53.5</v>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J67" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr"/>
@@ -7008,40 +5755,40 @@
     <row r="68" ht="64" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>-49</v>
+        <v>-47.8</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
+      <c r="J68" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
@@ -7049,12 +5796,12 @@
     <row r="69" ht="64" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
@@ -7072,7 +5819,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>-55</v>
+        <v>-53.7</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
@@ -7080,7 +5827,7 @@
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="125" t="inlineStr">
+      <c r="J69" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7090,19 +5837,19 @@
     <row r="70" ht="64" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -7113,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-51.8</v>
+        <v>-46.6</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -7121,7 +5868,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="125" t="inlineStr">
+      <c r="J70" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7131,12 +5878,12 @@
     <row r="71" ht="64" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
@@ -7154,15 +5901,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>-55.8</v>
+        <v>-51.7</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="125" t="inlineStr">
+      <c r="J71" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7172,19 +5919,19 @@
     <row r="72" ht="64" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -7195,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>-55.9</v>
+        <v>-60.5</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -7203,7 +5950,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="125" t="inlineStr">
+      <c r="J72" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7213,30 +5960,30 @@
     <row r="73" ht="64" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>-53.8</v>
+        <v>-49.2</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
@@ -7244,29 +5991,33 @@
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="inlineStr"/>
+      <c r="J73" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>in this test I deliberately  tried to cross read by sliding mugs over antennas like the plausiblity post deployement</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="64" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -7277,119 +6028,131 @@
         <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>-54.2</v>
+        <v>-60.8</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="J74" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="64" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>-45.1</v>
+        <v>-61.8</v>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr"/>
+      <c r="J75" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>in this test i tried keeping my hands on the mugs ith a wrist watch</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="64" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>-55.8</v>
+        <v>-52.1</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
+      <c r="J76" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>left my hands in while i fidigited with the mugs</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="64" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C77" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
@@ -7400,15 +6163,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>-57.1</v>
+        <v>-64.8</v>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="125" t="inlineStr">
+      <c r="J77" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7418,120 +6181,128 @@
     <row r="78" ht="64" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>E73842 -&gt; ant0</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>-54.5</v>
+        <v>-47.8</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73842</t>
+          <t>E28068940000503352E73442, E28068940000503352E73842</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
+      <c r="J78" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>slide one mug after the other</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="64" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F79" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>-54.7</v>
+        <v>-60.7</v>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr"/>
+      <c r="J79" s="84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>slid in both the mugs together at same time</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="64" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
         <v>316</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>-53.2</v>
+        <v>-60.4</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
+          <t>E28068940000503352E73842, E28068940000503352E73442</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="125" t="inlineStr">
+      <c r="J80" s="84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7541,30 +6312,30 @@
     <row r="81" ht="64" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>20260528-164756</t>
+          <t>20260529-093927</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>drip_tray_empty_cup_empty</t>
+          <t>drip_tray_half_full_cup_empty</t>
         </is>
       </c>
       <c r="C81" s="6" t="n">
         <v>316</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
+          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
         </is>
       </c>
       <c r="F81" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>-53.5</v>
+        <v>-43.2</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
@@ -7572,1645 +6343,16 @@
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K81" s="5" t="inlineStr"/>
-    </row>
-    <row r="82" ht="64" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>-56.1</v>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83" ht="64" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D83" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="6" t="n">
-        <v>-55.1</v>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84" ht="64" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>-55</v>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85" ht="64" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D85" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="6" t="n">
-        <v>-53.4</v>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86" ht="64" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>-51.6</v>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87" ht="64" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D87" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="E87" s="5" t="inlineStr"/>
-      <c r="F87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="6" t="inlineStr"/>
-      <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="117" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="inlineStr"/>
-    </row>
-    <row r="88" ht="64" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D88" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="117" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89" ht="64" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D89" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="6" t="n">
-        <v>-53.5</v>
-      </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90" ht="64" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D90" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>-51.1</v>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91" ht="64" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D91" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="6" t="n">
-        <v>-53</v>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92" ht="64" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>-56.3</v>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93" ht="64" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D93" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="6" t="n">
-        <v>-53.8</v>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94" ht="64" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D94" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>-55.4</v>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95" ht="64" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D95" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="6" t="n">
-        <v>-50.9</v>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96" ht="64" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D96" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>-53.9</v>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97" ht="64" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D97" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="6" t="n">
-        <v>-53.7</v>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98" ht="64" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>-54.4</v>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99" ht="64" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D99" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="6" t="n">
-        <v>-54.1</v>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr"/>
-    </row>
-    <row r="100" ht="64" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D100" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>-52.7</v>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101" ht="64" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D101" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="6" t="n">
-        <v>-55.7</v>
-      </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr"/>
-    </row>
-    <row r="102" ht="64" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D102" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>-51.2</v>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103" ht="64" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D103" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F103" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="6" t="n">
-        <v>-55.5</v>
-      </c>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I103" s="5" t="inlineStr"/>
-      <c r="J103" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K103" s="5" t="inlineStr"/>
-    </row>
-    <row r="104" ht="64" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>-52.8</v>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105" ht="64" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D105" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="6" t="n">
-        <v>-49.4</v>
-      </c>
-      <c r="H105" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I105" s="5" t="inlineStr"/>
-      <c r="J105" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr"/>
-    </row>
-    <row r="106" ht="64" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D106" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="117" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107" ht="64" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D107" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="E107" s="5" t="inlineStr"/>
-      <c r="F107" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="5" t="inlineStr"/>
-      <c r="I107" s="5" t="inlineStr"/>
-      <c r="J107" s="117" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr"/>
-    </row>
-    <row r="108" ht="64" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D108" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>-55.4</v>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109" ht="64" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D109" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="6" t="n">
-        <v>-54</v>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr"/>
-      <c r="J109" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr"/>
-    </row>
-    <row r="110" ht="64" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D110" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>-50.3</v>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111" ht="64" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D111" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E111" s="5" t="inlineStr"/>
-      <c r="F111" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="6" t="inlineStr"/>
-      <c r="H111" s="5" t="inlineStr"/>
-      <c r="I111" s="5" t="inlineStr"/>
-      <c r="J111" s="117" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="inlineStr"/>
-    </row>
-    <row r="112" ht="64" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>-56.3</v>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="64" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D113" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E113" s="5" t="inlineStr"/>
-      <c r="F113" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="6" t="inlineStr"/>
-      <c r="H113" s="5" t="inlineStr"/>
-      <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="117" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="64" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D114" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="3" t="n">
-        <v>-51.9</v>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="64" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D115" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F115" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="6" t="n">
-        <v>-54.2</v>
-      </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I115" s="5" t="inlineStr"/>
-      <c r="J115" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K115" s="5" t="inlineStr"/>
-    </row>
-    <row r="116" ht="64" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D116" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1, E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>-54.2</v>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117" ht="64" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D117" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F117" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" s="6" t="n">
-        <v>-50.6</v>
-      </c>
-      <c r="H117" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842, E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I117" s="5" t="inlineStr"/>
-      <c r="J117" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr"/>
-    </row>
-    <row r="118" ht="64" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D118" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>-60</v>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119" ht="64" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D119" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="6" t="n">
-        <v>-53.4</v>
-      </c>
-      <c r="H119" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I119" s="5" t="inlineStr"/>
-      <c r="J119" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr"/>
-    </row>
-    <row r="120" ht="64" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D120" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>-51.1</v>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="124" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121" ht="64" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="D121" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>E73442 -&gt; ant0, E73842 -&gt; ant1</t>
-        </is>
-      </c>
-      <c r="F121" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="6" t="n">
-        <v>-56.3</v>
-      </c>
-      <c r="H121" s="5" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73442, E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I121" s="5" t="inlineStr"/>
-      <c r="J121" s="125" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr"/>
-    </row>
-    <row r="122" ht="64" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>20260528-164756</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>drip_tray_empty_cup_empty</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>E73842 -&gt; ant0</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>E28068940000503352E73842</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="126" t="inlineStr">
-        <is>
-          <t>LOPSIDED</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr"/>
+      <c r="J81" s="85" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>slid in the mugs aproximately 60ms late</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
